--- a/colombres/Octubre/Octubre COLOMBRES 360.xlsx
+++ b/colombres/Octubre/Octubre COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\colombres\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835296B9-3ECB-455B-BB9D-CAC5408A7A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9577E97E-3A1F-4267-A8E8-AE889B01F6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$117</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="174">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -484,106 +484,74 @@
     <t>Titular: CONS. DE PROPIETARIOS COLOMBRES 360 Banco: SUPERVIELLE Sucursal: Lomas de Zamora CBU: 02700151 10040979780018 Nº de cuenta: 04097978-001 Código de Pago Electrónico: abonar con los centavos de la UF</t>
   </si>
   <si>
-    <t>VTO 15/10</t>
-  </si>
-  <si>
     <t>Mes de SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Mes de AGOSTO</t>
-  </si>
-  <si>
-    <t>Frank Matias Wallace - Mantenimiento ascensor AGOSTO</t>
-  </si>
-  <si>
-    <t>Transf 03/09</t>
-  </si>
-  <si>
-    <t>Transf 02/09</t>
-  </si>
-  <si>
-    <t>Debito 04/09</t>
-  </si>
-  <si>
-    <t>Transf 04/09</t>
-  </si>
-  <si>
-    <t>Frank Matias Wallace - Mantenimiento ascensor SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Fotocopias - tauge</t>
   </si>
   <si>
-    <t>Zafalonn Veronica - Reparacion bomba tango 20 inteligente</t>
-  </si>
-  <si>
-    <t>Transf 08/09</t>
-  </si>
-  <si>
-    <t>Debito 08/09</t>
-  </si>
-  <si>
-    <t>Debito 12/09</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza -  Mes de agosto</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza -  Mes de Septiembre</t>
-  </si>
-  <si>
-    <t>Salvatierra Matias - Desobstruccion trabajo columna 8B</t>
-  </si>
-  <si>
-    <t>Transf 11/09</t>
-  </si>
-  <si>
-    <t>Debito 23/09</t>
-  </si>
-  <si>
-    <t>Fumigacion Ortega Daniel Orlando mes de Junio</t>
-  </si>
-  <si>
-    <t>Transf 18/09</t>
-  </si>
-  <si>
-    <t>Vto. 1/10</t>
-  </si>
-  <si>
-    <t>Vto. 2/09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafalonn Veronica - Instalacion bomba elevadora </t>
-  </si>
-  <si>
-    <t>Debito 15/09</t>
-  </si>
-  <si>
-    <t>Transf 29/09</t>
-  </si>
-  <si>
-    <t>Fumigacion Septiembre - Viturro Alberto</t>
-  </si>
-  <si>
-    <t>AYRAM Cerrajeria - Pago en efectivo - Copia TAGS porteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uniforme Sr. Diego Calderon </t>
-  </si>
-  <si>
-    <t>Transf 23/09</t>
-  </si>
-  <si>
-    <t>Horas extras</t>
-  </si>
-  <si>
     <t>SI EN LA COLUMNA LLAMADA DEUDA O SALDO A FAVOR FIGURA UN NUMERO EN NEGATIVO SIGNIFICA QUE LA UF POSEE DINERO A FAVOR (ES DECIR PAGO DE MAS)</t>
   </si>
   <si>
-    <t>Deposito ya identificado 10/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> El deposito sin identificar de julio de 126 mil es de ella y el de agosto de $166.000 tambien</t>
+    <t>VTO 14/11</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza -  Mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>Debito 06/10</t>
+  </si>
+  <si>
+    <t>Transf 07/10</t>
+  </si>
+  <si>
+    <t>Debito 08/10</t>
+  </si>
+  <si>
+    <t>Transf 14/10</t>
+  </si>
+  <si>
+    <t>Transf 13/10</t>
+  </si>
+  <si>
+    <t>Liquidacion por Renuncia:</t>
+  </si>
+  <si>
+    <t>Debito 13/10</t>
+  </si>
+  <si>
+    <t>Debito 16/10</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Cambio de semaforo y cableado del mismo</t>
+  </si>
+  <si>
+    <t>Transf 17/10</t>
+  </si>
+  <si>
+    <t>Se debe octubre</t>
+  </si>
+  <si>
+    <t>Frank Matias Wallace - Mantenimiento ascensor - Se debe OCTUBRE</t>
+  </si>
+  <si>
+    <t>TecnoComp - Pagado por 3A - REPARACION ESTABILIZADOR PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TecnoComp - Pagado por 3A - CAMBIO DE DISCO RIGIDO 1 TB Y CONFIGURACION DVR </t>
+  </si>
+  <si>
+    <t>Claudia Guidobono</t>
+  </si>
+  <si>
+    <t>PABLO GARCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Raquel Martinez</t>
+  </si>
+  <si>
+    <t>Diego Varas</t>
   </si>
 </sst>
 </file>
@@ -1332,8 +1300,6 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1417,9 +1383,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1431,6 +1394,48 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1440,46 +1445,46 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1494,48 +1499,11 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1890,113 +1858,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L121"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="126" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="120"/>
+      <c r="B1" s="118"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="121" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-    </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="121" t="s">
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="119" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-    </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="163" t="s">
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+    </row>
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="150" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="122"/>
-      <c r="D4" s="122"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="163"/>
-      <c r="B5" s="163"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="163"/>
-      <c r="B6" s="163"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-    </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="163"/>
-      <c r="B7" s="163"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="162"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="162"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="164" t="s">
+      <c r="B4" s="150"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="150"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="150"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+    </row>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="150"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="147" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="147"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="147"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="151" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="164"/>
-      <c r="C14" s="164"/>
-      <c r="D14" s="164"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="164"/>
-      <c r="B15" s="164"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="164"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="164"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="164"/>
-      <c r="D16" s="164"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="164"/>
-      <c r="B17" s="164"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="164"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="151"/>
+      <c r="C14" s="151"/>
+      <c r="D14" s="151"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="151"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="151"/>
+      <c r="D15" s="151"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="151"/>
+      <c r="B16" s="151"/>
+      <c r="C16" s="151"/>
+      <c r="D16" s="151"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="151"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="151"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2004,7 +1972,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
         <v>80</v>
       </c>
@@ -2012,169 +1980,170 @@
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>131</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C23" s="115">
-        <v>1188974.7</v>
+        <v>151</v>
+      </c>
+      <c r="C23" s="113">
+        <v>1268327.8999999999</v>
       </c>
       <c r="D23" s="83"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="115">
-        <v>-232593.17</v>
+      <c r="C24" s="113">
+        <f>-523977.97+248116.64</f>
+        <v>-275861.32999999996</v>
       </c>
       <c r="D24" s="83"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="115">
-        <v>0.47</v>
+      <c r="C25" s="113">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D25" s="83"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="115"/>
+      <c r="C26" s="113"/>
       <c r="D26" s="83"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
         <v>82</v>
       </c>
       <c r="B27" s="49"/>
-      <c r="C27" s="116">
+      <c r="C27" s="114">
         <f>SUM(C23:C26)</f>
-        <v>956381.99999999988</v>
+        <v>992466.6399999999</v>
       </c>
       <c r="D27" s="84"/>
-      <c r="F27" s="160" t="s">
+      <c r="F27" s="145" t="s">
         <v>148</v>
       </c>
-      <c r="G27" s="161"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="127" t="s">
+      <c r="G27" s="146"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="125" t="s">
         <v>132</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="115">
-        <v>959379.6</v>
+        <v>151</v>
+      </c>
+      <c r="C28" s="113">
+        <v>971916.1</v>
       </c>
       <c r="D28" s="83"/>
-      <c r="F28" s="160"/>
-      <c r="G28" s="161"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F28" s="145"/>
+      <c r="G28" s="146"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="111">
-        <v>-208665.08</v>
+      <c r="C29" s="109">
+        <v>-211391.74</v>
       </c>
       <c r="D29" s="83"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="111">
-        <v>0.48</v>
+      <c r="C30" s="109">
+        <v>0.64</v>
       </c>
       <c r="D30" s="83"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>161</v>
+      </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="111"/>
+      <c r="C31" s="109">
+        <v>862842</v>
+      </c>
       <c r="D31" s="83"/>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="49" t="s">
         <v>82</v>
       </c>
       <c r="B32" s="49"/>
       <c r="C32" s="50">
         <f>SUM(C28:C31)</f>
-        <v>750715</v>
+        <v>1623367</v>
       </c>
       <c r="D32" s="84"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>130</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C33" s="115">
-        <v>971695.69</v>
-      </c>
-      <c r="D33" s="126"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="C33" s="113">
+        <v>1034599.1</v>
+      </c>
+      <c r="D33" s="124"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="115">
-        <v>-211343.82</v>
-      </c>
-      <c r="D34" s="126"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C34" s="113">
+        <v>-225025.29</v>
+      </c>
+      <c r="D34" s="124"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="115">
-        <v>0.13</v>
-      </c>
-      <c r="D35" s="126"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
-        <v>181</v>
-      </c>
+      <c r="C35" s="113">
+        <v>0.19</v>
+      </c>
+      <c r="D35" s="124"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="111">
-        <v>17000</v>
-      </c>
-      <c r="D36" s="126"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C36" s="109"/>
+      <c r="D36" s="124"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="125"/>
+      <c r="B37" s="123"/>
       <c r="C37" s="50">
         <f>SUM(C33:C36)</f>
-        <v>777351.99999999988</v>
+        <v>809573.99999999988</v>
       </c>
       <c r="D37" s="84"/>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>0</v>
       </c>
@@ -2182,12 +2151,12 @@
       <c r="C38" s="20"/>
       <c r="D38" s="85">
         <f>C27+C32+C37</f>
-        <v>2484449</v>
+        <v>3425407.6399999997</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
         <v>38</v>
       </c>
@@ -2196,46 +2165,43 @@
       <c r="D39" s="86"/>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="115">
-        <v>90000</v>
-      </c>
-      <c r="D40" s="124" t="s">
-        <v>158</v>
+      <c r="C40" s="113">
+        <f>35000*3</f>
+        <v>105000</v>
+      </c>
+      <c r="D40" s="180" t="s">
+        <v>159</v>
       </c>
       <c r="G40" s="14"/>
     </row>
-    <row r="41" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="129" t="s">
+    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="127" t="s">
         <v>133</v>
       </c>
-      <c r="B41" s="119" t="s">
-        <v>152</v>
-      </c>
-      <c r="C41" s="115">
-        <v>195000</v>
-      </c>
-      <c r="D41" s="87" t="s">
-        <v>176</v>
-      </c>
+      <c r="B41" s="117" t="s">
+        <v>166</v>
+      </c>
+      <c r="C41" s="113"/>
+      <c r="D41" s="180"/>
       <c r="G41" s="14"/>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="31"/>
-      <c r="D42" s="88">
+      <c r="D42" s="85">
         <f>SUM(C40:C41)</f>
-        <v>285000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
         <v>77</v>
       </c>
@@ -2243,717 +2209,620 @@
       <c r="C43" s="29"/>
       <c r="D43" s="60"/>
     </row>
-    <row r="44" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="151" t="s">
+    <row r="44" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="148" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="152"/>
-      <c r="C44" s="145">
+      <c r="B44" s="149"/>
+      <c r="C44" s="142">
         <v>175052</v>
       </c>
-      <c r="D44" s="112" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="151" t="s">
+      <c r="D44" s="110" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="148" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="152"/>
-      <c r="C45" s="146">
+      <c r="B45" s="149"/>
+      <c r="C45" s="143">
         <v>4203</v>
       </c>
-      <c r="D45" s="112" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D45" s="110" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="18" t="s">
         <v>1</v>
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="31"/>
-      <c r="D46" s="89">
+      <c r="D46" s="87">
         <f>SUM(C44:C45)</f>
         <v>179255</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="27" t="s">
         <v>35</v>
       </c>
       <c r="B47" s="19"/>
       <c r="C47" s="32"/>
-      <c r="D47" s="90"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D47" s="88"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>134</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C48" s="147">
-        <v>1349845.83</v>
-      </c>
-      <c r="D48" s="112" t="s">
-        <v>163</v>
-      </c>
-      <c r="F48" s="130"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="C48" s="144">
+        <v>1424079.5</v>
+      </c>
+      <c r="D48" s="110" t="s">
+        <v>158</v>
+      </c>
+      <c r="F48" s="128"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>135</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C49" s="144">
-        <v>15600.25</v>
-      </c>
-      <c r="D49" s="112" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="C49" s="141">
+        <v>16459.22</v>
+      </c>
+      <c r="D49" s="110" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>136</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C50" s="144">
-        <v>140402.25</v>
-      </c>
-      <c r="D50" s="112" t="str">
+        <v>151</v>
+      </c>
+      <c r="C50" s="141">
+        <v>148132.94</v>
+      </c>
+      <c r="D50" s="110" t="str">
         <f>D49</f>
-        <v>Debito 12/09</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+        <v>Debito 13/10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C51" s="144">
-        <v>277719.27</v>
-      </c>
-      <c r="D51" s="113" t="str">
+        <v>151</v>
+      </c>
+      <c r="C51" s="141">
+        <v>290229.78999999998</v>
+      </c>
+      <c r="D51" s="111" t="str">
         <f>D50</f>
-        <v>Debito 12/09</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 13/10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="18" t="s">
         <v>2</v>
       </c>
       <c r="B52" s="19"/>
       <c r="C52" s="33"/>
-      <c r="D52" s="89">
+      <c r="D52" s="87">
         <f>SUM(C48:C51)</f>
-        <v>1783567.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1878901.45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
         <v>37</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="32"/>
-      <c r="D53" s="90"/>
-    </row>
-    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D53" s="88"/>
+    </row>
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>138</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C54" s="144">
-        <v>495884.57</v>
-      </c>
-      <c r="D54" s="94" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>138</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C55" s="144">
-        <v>512267.77</v>
-      </c>
-      <c r="D55" s="141" t="s">
+      <c r="B54" s="5"/>
+      <c r="C54" s="141"/>
+      <c r="D54" s="138"/>
+    </row>
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="5"/>
+      <c r="C55" s="141">
+        <v>35883.19</v>
+      </c>
+      <c r="D55" s="111" t="s">
+        <v>160</v>
+      </c>
+      <c r="F55">
+        <f>180000+82000</f>
+        <v>262000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="141">
+        <v>728258.14</v>
+      </c>
+      <c r="D56" s="92" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="157" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" s="158"/>
+      <c r="C57" s="141"/>
+      <c r="D57" s="122"/>
+    </row>
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" s="133"/>
+      <c r="C58" s="122">
+        <v>262000</v>
+      </c>
+      <c r="D58" s="122" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="116"/>
+      <c r="C59" s="141"/>
+      <c r="D59" s="122"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="18"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="87">
+        <f>SUM(C54:C59)</f>
+        <v>1026141.3300000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="18"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="90"/>
+    </row>
+    <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="132" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="133"/>
+      <c r="C62" s="141">
+        <v>11200</v>
+      </c>
+      <c r="D62" s="134" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="148" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63" s="149"/>
+      <c r="C63" s="141">
+        <v>15000</v>
+      </c>
+      <c r="D63" s="181"/>
+    </row>
+    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="148" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="144">
-        <v>35957.85</v>
-      </c>
-      <c r="D56" s="113" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="144">
-        <v>728258.14</v>
-      </c>
-      <c r="D57" s="94" t="s">
+      <c r="B64" s="149"/>
+      <c r="C64" s="141">
+        <v>175000</v>
+      </c>
+      <c r="D64" s="181"/>
+    </row>
+    <row r="65" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="155" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="158" t="s">
-        <v>159</v>
-      </c>
-      <c r="B58" s="159"/>
-      <c r="C58" s="144">
-        <v>158501</v>
-      </c>
-      <c r="D58" s="124" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="158" t="s">
-        <v>154</v>
-      </c>
-      <c r="B59" s="159"/>
-      <c r="C59" s="144">
-        <v>158501</v>
-      </c>
-      <c r="D59" s="124" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="140" t="s">
-        <v>167</v>
-      </c>
-      <c r="B60" s="135"/>
-      <c r="C60" s="144">
-        <v>24100</v>
-      </c>
-      <c r="D60" s="124" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="140" t="s">
-        <v>170</v>
-      </c>
-      <c r="B61" s="135"/>
-      <c r="C61" s="144">
-        <v>25600</v>
-      </c>
-      <c r="D61" s="124" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="140" t="s">
-        <v>177</v>
-      </c>
-      <c r="B62" s="135"/>
-      <c r="C62" s="144">
-        <v>50000</v>
-      </c>
-      <c r="D62" s="87" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B63" s="135"/>
-      <c r="C63" s="144">
-        <v>130000</v>
-      </c>
-      <c r="D63" s="124" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B64" s="118"/>
-      <c r="C64" s="144">
-        <v>310000</v>
-      </c>
-      <c r="D64" s="124" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="18"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="89">
-        <f>SUM(C54:C64)</f>
-        <v>2629070.33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="92"/>
-    </row>
-    <row r="67" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="134" t="s">
-        <v>160</v>
-      </c>
-      <c r="B67" s="135"/>
-      <c r="C67" s="144">
-        <f>4800+5700</f>
-        <v>10500</v>
-      </c>
-      <c r="D67" s="136" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="134" t="s">
-        <v>179</v>
-      </c>
-      <c r="B68" s="135"/>
-      <c r="C68" s="144">
-        <v>115995</v>
-      </c>
-      <c r="D68" s="124" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="140" t="s">
-        <v>178</v>
-      </c>
-      <c r="B69" s="135"/>
-      <c r="C69" s="144">
-        <v>10000</v>
-      </c>
-      <c r="D69" s="136" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="156" t="s">
+      <c r="B65" s="156"/>
+      <c r="C65" s="144">
+        <v>67950</v>
+      </c>
+      <c r="D65" s="122" t="s">
         <v>165</v>
       </c>
-      <c r="B70" s="157"/>
-      <c r="C70" s="144">
-        <v>107100</v>
-      </c>
-      <c r="D70" s="124" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="156" t="s">
-        <v>166</v>
-      </c>
-      <c r="B71" s="157"/>
-      <c r="C71" s="147">
-        <v>93900</v>
-      </c>
-      <c r="D71" s="124" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="18" t="s">
+    </row>
+    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B72" s="27"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="96">
-        <f>SUM(C67:C67)</f>
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="27" t="s">
+      <c r="B66" s="27"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="94">
+        <f>SUM(C62:C62)</f>
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B73" s="59"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="92"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
+      <c r="B67" s="59"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="90"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="144">
+      <c r="B68" s="5"/>
+      <c r="C68" s="141">
         <v>56820.35</v>
       </c>
-      <c r="D74" s="97"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
+      <c r="D68" s="95"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="144">
-        <v>100718.93</v>
-      </c>
-      <c r="D75" s="95"/>
-    </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="45" t="s">
+      <c r="B69" s="5"/>
+      <c r="C69" s="141">
+        <v>80545.34</v>
+      </c>
+      <c r="D69" s="93"/>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B76" s="45"/>
-      <c r="C76" s="98"/>
-      <c r="D76" s="89">
-        <f>SUM(C74:C75)</f>
-        <v>157539.28</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="83"/>
-      <c r="D77" s="99"/>
-    </row>
-    <row r="78" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="153" t="s">
+      <c r="B70" s="45"/>
+      <c r="C70" s="96"/>
+      <c r="D70" s="87">
+        <f>SUM(C68:C69)</f>
+        <v>137365.69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="83"/>
+      <c r="D71" s="97"/>
+    </row>
+    <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="152" t="s">
         <v>147</v>
       </c>
-      <c r="B78" s="154"/>
-      <c r="C78" s="155"/>
-      <c r="D78" s="100"/>
-    </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="1"/>
-      <c r="C79" s="101"/>
-      <c r="D79" s="102"/>
-      <c r="E79" s="40"/>
-    </row>
-    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
+      <c r="B72" s="153"/>
+      <c r="C72" s="154"/>
+      <c r="D72" s="98">
+        <f>7000000-6763271.11</f>
+        <v>236728.88999999966</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="C73" s="99"/>
+      <c r="D73" s="100"/>
+      <c r="E73" s="40"/>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B80" s="10"/>
-      <c r="C80" s="103"/>
-      <c r="D80" s="104">
-        <f>(SUM(D29:D78))</f>
-        <v>7529381.21</v>
-      </c>
-      <c r="E80" s="40"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C81" s="101"/>
-      <c r="D81" s="101"/>
-      <c r="F81" s="133"/>
-    </row>
-    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C82" s="101"/>
-      <c r="D82" s="101"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="11" t="s">
+      <c r="B74" s="10"/>
+      <c r="C74" s="101"/>
+      <c r="D74" s="102">
+        <f>(SUM(D29:D72))</f>
+        <v>7000000</v>
+      </c>
+      <c r="E74" s="40"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C75" s="99"/>
+      <c r="D75" s="99"/>
+      <c r="F75" s="131"/>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="99"/>
+      <c r="D76" s="99"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B83" s="12"/>
-      <c r="C83" s="105"/>
-      <c r="D83" s="106"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="151"/>
-      <c r="B84" s="152"/>
-      <c r="C84" s="93"/>
-      <c r="D84" s="91"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="151"/>
-      <c r="B85" s="152"/>
-      <c r="C85" s="93"/>
-      <c r="D85" s="91"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="109"/>
-      <c r="B86" s="110"/>
-      <c r="C86" s="93"/>
-      <c r="D86" s="91"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="43"/>
-      <c r="B87" s="42"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51">
-        <f>SUM(C84:C86)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="21" t="s">
+      <c r="B77" s="12"/>
+      <c r="C77" s="103"/>
+      <c r="D77" s="104"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="148"/>
+      <c r="B78" s="149"/>
+      <c r="C78" s="91"/>
+      <c r="D78" s="89"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="148"/>
+      <c r="B79" s="149"/>
+      <c r="C79" s="91"/>
+      <c r="D79" s="89"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="107"/>
+      <c r="B80" s="108"/>
+      <c r="C80" s="91"/>
+      <c r="D80" s="89"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="43"/>
+      <c r="B81" s="42"/>
+      <c r="C81" s="51"/>
+      <c r="D81" s="51">
+        <f>SUM(C78:C80)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B90" s="21"/>
-      <c r="C90" s="22"/>
-      <c r="D90" s="117"/>
-    </row>
-    <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
+      <c r="B84" s="21"/>
+      <c r="C84" s="22"/>
+      <c r="D84" s="115"/>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B92" s="10"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="61">
-        <f>D87+D90</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="81" t="s">
+      <c r="B86" s="10"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="61">
+        <f>D81+D84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="B94" s="82">
-        <f>D80</f>
-        <v>7529381.21</v>
-      </c>
-      <c r="C94" s="40"/>
-    </row>
-    <row r="95" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="81" t="s">
+      <c r="B88" s="82">
+        <f>D74</f>
+        <v>7000000</v>
+      </c>
+      <c r="C88" s="40"/>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="B95" s="82">
-        <f>D80-D78</f>
-        <v>7529381.21</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="81" t="s">
+      <c r="B89" s="82">
+        <f>D74-D72</f>
+        <v>6763271.1100000003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="B96" s="82">
-        <f>D92-D90</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81" t="s">
+      <c r="B90" s="82">
+        <f>D86-D84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="B97" s="82">
-        <f>D92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="150"/>
-      <c r="B100" s="150"/>
-      <c r="C100" s="150"/>
-      <c r="D100" s="150"/>
-    </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="150"/>
-      <c r="B101" s="150"/>
-      <c r="C101" s="150"/>
-      <c r="D101" s="150"/>
-    </row>
-    <row r="102" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="150"/>
-      <c r="B102" s="150"/>
-      <c r="C102" s="150"/>
-      <c r="D102" s="150"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="15" t="s">
+      <c r="B91" s="82">
+        <f>D86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="161"/>
+      <c r="B94" s="161"/>
+      <c r="C94" s="161"/>
+      <c r="D94" s="161"/>
+    </row>
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="161"/>
+      <c r="B95" s="161"/>
+      <c r="C95" s="161"/>
+      <c r="D95" s="161"/>
+    </row>
+    <row r="96" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="161"/>
+      <c r="B96" s="161"/>
+      <c r="C96" s="161"/>
+      <c r="D96" s="161"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B104" s="36"/>
-    </row>
-    <row r="105" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="24" t="s">
+      <c r="B98" s="36"/>
+    </row>
+    <row r="99" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B105" s="114">
-        <v>4445058.1599999992</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="16" t="s">
+      <c r="B99" s="112">
+        <v>3268631.95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B106" s="37">
+      <c r="B100" s="37">
         <f>PRORRATEO!H34</f>
-        <v>6772536</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="16" t="s">
+        <v>7504571.0899999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B107" s="95">
-        <f>B123</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B108" s="138">
-        <v>-366010</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="17" t="s">
+      <c r="B101" s="93">
+        <f>B116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="B109" s="138">
-        <f>-16000-21903-15668</f>
-        <v>-53571</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="35" t="s">
+      <c r="B102" s="136">
+        <v>-46641</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B110" s="95">
-        <f>-B95</f>
-        <v>-7529381.21</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="17" t="s">
+      <c r="B103" s="93">
+        <f>-B89</f>
+        <v>-6763271.1100000003</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B111" s="95">
-        <f>-(B96)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="23" t="s">
+      <c r="B104" s="93">
+        <f>-(B90)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B112" s="114">
-        <f>SUM(B105:B111)</f>
-        <v>3268631.95</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="38"/>
-      <c r="C113" s="40"/>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A115" s="149" t="s">
+      <c r="B105" s="112">
+        <f>SUM(B99:B104)</f>
+        <v>3963290.9299999988</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="38"/>
+      <c r="C106" s="40"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="160" t="s">
         <v>78</v>
       </c>
-      <c r="B115" s="149"/>
-    </row>
-    <row r="116" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="149"/>
-      <c r="B116" s="149"/>
-    </row>
-    <row r="117" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="107"/>
-      <c r="B117" s="30"/>
-    </row>
-    <row r="118" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="107"/>
-      <c r="B118" s="30"/>
-    </row>
-    <row r="119" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="107"/>
-      <c r="B119" s="30"/>
-    </row>
-    <row r="120" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="107"/>
-      <c r="B120" s="30"/>
-    </row>
-    <row r="121" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="107"/>
-      <c r="B121" s="30"/>
-    </row>
-    <row r="122" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="107"/>
-      <c r="B122" s="131"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="41" t="s">
+      <c r="B108" s="160"/>
+    </row>
+    <row r="109" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="160"/>
+      <c r="B109" s="160"/>
+    </row>
+    <row r="110" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="105"/>
+      <c r="B110" s="30"/>
+    </row>
+    <row r="111" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="105"/>
+      <c r="B111" s="30"/>
+    </row>
+    <row r="112" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="105"/>
+      <c r="B112" s="30"/>
+    </row>
+    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="105"/>
+      <c r="B113" s="30"/>
+    </row>
+    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="105"/>
+      <c r="B114" s="30"/>
+    </row>
+    <row r="115" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="105"/>
+      <c r="B115" s="129"/>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B123" s="108">
-        <f>SUM(B117:B122)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L124" s="8"/>
-    </row>
-    <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="148"/>
-      <c r="B125" s="148"/>
-      <c r="C125" s="148"/>
-      <c r="D125" s="148"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A126" s="148"/>
-      <c r="B126" s="148"/>
-      <c r="C126" s="148"/>
-      <c r="D126" s="148"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="148"/>
-      <c r="B127" s="148"/>
-      <c r="C127" s="148"/>
-      <c r="D127" s="148"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" s="148"/>
-      <c r="B128" s="148"/>
-      <c r="C128" s="148"/>
-      <c r="D128" s="148"/>
+      <c r="B116" s="106">
+        <f>SUM(B110:B115)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L117" s="8"/>
+    </row>
+    <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="159"/>
+      <c r="B118" s="159"/>
+      <c r="C118" s="159"/>
+      <c r="D118" s="159"/>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" s="159"/>
+      <c r="B119" s="159"/>
+      <c r="C119" s="159"/>
+      <c r="D119" s="159"/>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" s="159"/>
+      <c r="B120" s="159"/>
+      <c r="C120" s="159"/>
+      <c r="D120" s="159"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="159"/>
+      <c r="B121" s="159"/>
+      <c r="C121" s="159"/>
+      <c r="D121" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A118:D121"/>
+    <mergeCell ref="A108:B109"/>
+    <mergeCell ref="A94:D96"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="F27:G28"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A125:D128"/>
-    <mergeCell ref="A115:B116"/>
-    <mergeCell ref="A100:D102"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A84:B84"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2964,84 +2833,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="0.109375" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="171" t="s">
+      <c r="B1" s="162" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
+      <c r="I2" s="162"/>
+      <c r="J2" s="162"/>
+      <c r="K2" s="162"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="132">
+      <c r="O2" s="130">
         <v>7000000</v>
       </c>
       <c r="P2" s="47"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="172"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3050,79 +2919,79 @@
       <c r="O3" s="48"/>
       <c r="P3" s="52"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="165" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="176" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="169" t="s">
+      <c r="C4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="169" t="s">
+      <c r="D4" s="166" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="169" t="s">
+      <c r="E4" s="166" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="169" t="s">
+      <c r="F4" s="166" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="169" t="s">
+      <c r="G4" s="166" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="169" t="s">
+      <c r="H4" s="166" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="169" t="s">
+      <c r="I4" s="166" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="178" t="s">
+      <c r="J4" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="176" t="s">
+      <c r="K4" s="168" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="176" t="s">
+      <c r="L4" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="176" t="s">
+      <c r="M4" s="168" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="181" t="s">
+      <c r="N4" s="174" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="173" t="s">
+      <c r="P4" s="164" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="40"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="166"/>
-      <c r="B5" s="168"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="177"/>
+      <c r="B5" s="179"/>
       <c r="C5" s="170"/>
       <c r="D5" s="170"/>
-      <c r="E5" s="175"/>
+      <c r="E5" s="167"/>
       <c r="F5" s="170"/>
       <c r="G5" s="170"/>
       <c r="H5" s="170"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="177"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="177"/>
-      <c r="N5" s="182"/>
+      <c r="I5" s="167"/>
+      <c r="J5" s="172"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="173"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="175"/>
       <c r="O5" s="53" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 15/10</v>
-      </c>
-      <c r="P5" s="174"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>VTO 14/11</v>
+      </c>
+      <c r="P5" s="165"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3140,19 +3009,19 @@
         <v>4.57</v>
       </c>
       <c r="G6" s="63">
-        <v>324900.01</v>
+        <v>309800.01</v>
       </c>
       <c r="H6" s="64">
-        <v>335000</v>
+        <v>300000</v>
       </c>
       <c r="I6" s="65"/>
       <c r="J6" s="66">
         <f>G6-H6</f>
-        <v>-10099.989999999991</v>
+        <v>9800.0100000000093</v>
       </c>
       <c r="K6" s="66">
         <f>IF(J6&gt;0,J6*2.95%,0)</f>
-        <v>0</v>
+        <v>289.1002950000003</v>
       </c>
       <c r="L6" s="67">
         <f>O$3*F6%</f>
@@ -3167,17 +3036,17 @@
       </c>
       <c r="O6" s="69">
         <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>309800.01</v>
+        <v>329989.01</v>
       </c>
       <c r="P6" s="70">
         <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
-        <v>319094.01</v>
+        <v>339889.01</v>
       </c>
       <c r="Q6" s="40">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -3195,17 +3064,19 @@
         <v>3.07</v>
       </c>
       <c r="G7" s="63">
-        <v>219900.02</v>
-      </c>
-      <c r="H7" s="64"/>
+        <v>441287.02</v>
+      </c>
+      <c r="H7" s="64">
+        <v>214900</v>
+      </c>
       <c r="I7" s="65"/>
       <c r="J7" s="66">
         <f t="shared" ref="J7:J31" si="2">G7-H7</f>
-        <v>219900.02</v>
+        <v>226387.02000000002</v>
       </c>
       <c r="K7" s="66">
         <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
-        <v>6487.0505899999998</v>
+        <v>6678.4170900000008</v>
       </c>
       <c r="L7" s="67">
         <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
@@ -3220,19 +3091,21 @@
       </c>
       <c r="O7" s="69">
         <f t="shared" si="0"/>
-        <v>441287.02</v>
+        <v>447965.02</v>
       </c>
       <c r="P7" s="70">
         <f t="shared" si="1"/>
-        <v>454526.02</v>
+        <v>461404.02</v>
       </c>
       <c r="Q7" s="40">
         <f>Q6+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="R7" s="40"/>
-    </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3242,7 +3115,7 @@
       <c r="C8" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="139" t="s">
+      <c r="D8" s="137" t="s">
         <v>149</v>
       </c>
       <c r="E8" s="57"/>
@@ -3250,19 +3123,19 @@
         <v>4.55</v>
       </c>
       <c r="G8" s="63">
-        <v>2140634.0299999998</v>
+        <v>2192843.0299999998</v>
       </c>
       <c r="H8" s="64">
-        <v>320000</v>
+        <v>318500</v>
       </c>
       <c r="I8" s="65"/>
       <c r="J8" s="66">
         <f t="shared" si="2"/>
-        <v>1820634.0299999998</v>
+        <v>1874343.0299999998</v>
       </c>
       <c r="K8" s="66">
         <f t="shared" si="3"/>
-        <v>53708.703884999995</v>
+        <v>55293.119384999998</v>
       </c>
       <c r="L8" s="67">
         <f t="shared" si="4"/>
@@ -3277,18 +3150,18 @@
       </c>
       <c r="O8" s="69">
         <f t="shared" si="0"/>
-        <v>2192843.0299999998</v>
+        <v>2248136.0299999998</v>
       </c>
       <c r="P8" s="70">
         <f t="shared" si="1"/>
-        <v>2258628.0299999998</v>
+        <v>2315580.0299999998</v>
       </c>
       <c r="Q8" s="40">
         <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -3306,15 +3179,15 @@
         <v>3.05</v>
       </c>
       <c r="G9" s="63">
-        <v>132402.04</v>
+        <v>191479.04000000001</v>
       </c>
       <c r="H9" s="64">
-        <v>160000</v>
+        <v>220000</v>
       </c>
       <c r="I9" s="65"/>
       <c r="J9" s="66">
         <f t="shared" si="2"/>
-        <v>-27597.959999999992</v>
+        <v>-28520.959999999992</v>
       </c>
       <c r="K9" s="66">
         <f t="shared" si="3"/>
@@ -3333,11 +3206,11 @@
       </c>
       <c r="O9" s="69">
         <f t="shared" si="0"/>
-        <v>185902.04</v>
+        <v>184979.04</v>
       </c>
       <c r="P9" s="70">
         <f t="shared" si="1"/>
-        <v>191479.04000000001</v>
+        <v>190528.04</v>
       </c>
       <c r="Q9" s="40">
         <f t="shared" si="6"/>
@@ -3348,7 +3221,7 @@
       </c>
       <c r="S9" s="40"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3366,15 +3239,16 @@
         <v>4.55</v>
       </c>
       <c r="G10" s="63">
-        <v>318348.05</v>
+        <v>316848.05</v>
       </c>
       <c r="H10" s="64">
-        <v>320000</v>
+        <f>127000+RESUMEN!C63+RESUMEN!C64</f>
+        <v>317000</v>
       </c>
       <c r="I10" s="65"/>
       <c r="J10" s="66">
         <f t="shared" si="2"/>
-        <v>-1651.9500000000116</v>
+        <v>-151.95000000001164</v>
       </c>
       <c r="K10" s="66">
         <f t="shared" si="3"/>
@@ -3393,11 +3267,11 @@
       </c>
       <c r="O10" s="69">
         <f t="shared" si="0"/>
-        <v>316848.05</v>
+        <v>318348.05</v>
       </c>
       <c r="P10" s="70">
         <f t="shared" si="1"/>
-        <v>326353.05</v>
+        <v>327898.05</v>
       </c>
       <c r="Q10" s="40">
         <f t="shared" si="6"/>
@@ -3405,7 +3279,7 @@
       </c>
       <c r="S10" s="40"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -3423,16 +3297,15 @@
         <v>3.05</v>
       </c>
       <c r="G11" s="63">
-        <v>207370.06</v>
+        <v>213500.06</v>
       </c>
       <c r="H11" s="64">
-        <f>G11</f>
-        <v>207370.06</v>
+        <v>219905.06</v>
       </c>
       <c r="I11" s="65"/>
       <c r="J11" s="66">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-6405</v>
       </c>
       <c r="K11" s="66">
         <f t="shared" si="3"/>
@@ -3451,28 +3324,28 @@
       </c>
       <c r="O11" s="69">
         <f t="shared" si="0"/>
-        <v>213500.06</v>
+        <v>207095.06</v>
       </c>
       <c r="P11" s="70">
         <f t="shared" si="1"/>
-        <v>219905.06</v>
+        <v>213308.06</v>
       </c>
       <c r="Q11" s="40">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="56">
         <v>7</v>
       </c>
-      <c r="C12" s="137" t="s">
+      <c r="C12" s="135" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="137" t="s">
+      <c r="D12" s="135" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="56"/>
@@ -3480,20 +3353,19 @@
         <v>4.55</v>
       </c>
       <c r="G12" s="63">
-        <v>335668.07</v>
+        <v>318500.07</v>
       </c>
       <c r="H12" s="64">
-        <f>15668+320000</f>
-        <v>335668</v>
+        <v>320000</v>
       </c>
       <c r="I12" s="65"/>
       <c r="J12" s="66">
         <f t="shared" si="2"/>
-        <v>7.0000000006984919E-2</v>
+        <v>-1499.929999999993</v>
       </c>
       <c r="K12" s="66">
         <f t="shared" si="3"/>
-        <v>2.0650000002060552E-3</v>
+        <v>0</v>
       </c>
       <c r="L12" s="67">
         <f t="shared" si="4"/>
@@ -3508,20 +3380,20 @@
       </c>
       <c r="O12" s="69">
         <f t="shared" si="0"/>
-        <v>318500.07</v>
+        <v>317000.07</v>
       </c>
       <c r="P12" s="70">
         <f t="shared" si="1"/>
-        <v>328055.07</v>
+        <v>326510.07</v>
       </c>
       <c r="Q12" s="40">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R12" s="133"/>
-      <c r="S12" s="130"/>
-    </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="131"/>
+      <c r="S12" s="128"/>
+    </row>
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3539,20 +3411,19 @@
         <v>3.05</v>
       </c>
       <c r="G13" s="63">
-        <v>601413.07999999996</v>
+        <v>213500.08</v>
       </c>
       <c r="H13" s="64">
-        <f>366010+213500+21903</f>
-        <v>601413</v>
+        <v>219305.08</v>
       </c>
       <c r="I13" s="65"/>
       <c r="J13" s="66">
         <f t="shared" si="2"/>
-        <v>7.9999999958090484E-2</v>
+        <v>-5805</v>
       </c>
       <c r="K13" s="66">
         <f t="shared" si="3"/>
-        <v>2.3599999987636696E-3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="67">
         <f t="shared" si="4"/>
@@ -3567,18 +3438,18 @@
       </c>
       <c r="O13" s="69">
         <f t="shared" si="0"/>
-        <v>213500.08</v>
+        <v>207695.08</v>
       </c>
       <c r="P13" s="70">
         <f t="shared" si="1"/>
-        <v>219905.08</v>
+        <v>213926.08</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3596,20 +3467,20 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="G14" s="63">
-        <v>335677.09</v>
-      </c>
-      <c r="H14" s="142">
-        <f>16000+320000-323</f>
-        <v>335677</v>
+        <v>319200.09000000003</v>
+      </c>
+      <c r="H14" s="139">
+        <f>176000+80000+64000</f>
+        <v>320000</v>
       </c>
       <c r="I14" s="65"/>
       <c r="J14" s="66">
         <f t="shared" si="2"/>
-        <v>9.0000000025611371E-2</v>
+        <v>-799.90999999997439</v>
       </c>
       <c r="K14" s="66">
         <f t="shared" si="3"/>
-        <v>2.6550000007555356E-3</v>
+        <v>0</v>
       </c>
       <c r="L14" s="67">
         <f t="shared" si="4"/>
@@ -3624,18 +3495,21 @@
       </c>
       <c r="O14" s="69">
         <f t="shared" si="0"/>
-        <v>319200.09000000003</v>
+        <v>318400.09000000003</v>
       </c>
       <c r="P14" s="70">
         <f t="shared" si="1"/>
-        <v>328776.09000000003</v>
+        <v>327952.09000000003</v>
       </c>
       <c r="Q14" s="40">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3653,17 +3527,19 @@
         <v>3.05</v>
       </c>
       <c r="G15" s="63">
-        <v>213500.1</v>
-      </c>
-      <c r="H15" s="64"/>
+        <v>438298.1</v>
+      </c>
+      <c r="H15" s="64">
+        <v>213500</v>
+      </c>
       <c r="I15" s="65"/>
       <c r="J15" s="66">
         <f t="shared" si="2"/>
-        <v>213500.1</v>
+        <v>224798.09999999998</v>
       </c>
       <c r="K15" s="66">
         <f t="shared" si="3"/>
-        <v>6298.252950000001</v>
+        <v>6631.5439499999993</v>
       </c>
       <c r="L15" s="67">
         <f t="shared" si="4"/>
@@ -3674,22 +3550,25 @@
         <v>213500</v>
       </c>
       <c r="N15" s="68">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="O15" s="69">
         <f t="shared" si="0"/>
-        <v>438298.1</v>
+        <v>444930.1</v>
       </c>
       <c r="P15" s="70">
         <f t="shared" si="1"/>
-        <v>451447.1</v>
+        <v>458278.1</v>
       </c>
       <c r="Q15" s="40">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R15" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3746,7 +3625,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3764,19 +3643,20 @@
         <v>3.05</v>
       </c>
       <c r="G17" s="63">
-        <v>209141.12</v>
+        <v>212641.12</v>
       </c>
       <c r="H17" s="64">
-        <v>210000</v>
+        <f>166000+46641</f>
+        <v>212641</v>
       </c>
       <c r="I17" s="65"/>
       <c r="J17" s="66">
         <f t="shared" si="2"/>
-        <v>-858.88000000000466</v>
+        <v>0.11999999999534339</v>
       </c>
       <c r="K17" s="66">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3.53999999986263E-3</v>
       </c>
       <c r="L17" s="67">
         <f t="shared" si="4"/>
@@ -3791,21 +3671,18 @@
       </c>
       <c r="O17" s="69">
         <f t="shared" si="0"/>
-        <v>212641.12</v>
+        <v>213500.12</v>
       </c>
       <c r="P17" s="70">
         <f t="shared" si="1"/>
-        <v>219020.12</v>
+        <v>219905.12</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
-      <c r="R17" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3823,15 +3700,15 @@
         <v>4.55</v>
       </c>
       <c r="G18" s="63">
-        <v>318500.13</v>
+        <v>308945.13</v>
       </c>
       <c r="H18" s="65">
-        <v>328055.13</v>
+        <v>318213.13</v>
       </c>
       <c r="I18" s="65"/>
       <c r="J18" s="66">
         <f t="shared" si="2"/>
-        <v>-9555</v>
+        <v>-9268</v>
       </c>
       <c r="K18" s="66">
         <f t="shared" si="3"/>
@@ -3850,18 +3727,18 @@
       </c>
       <c r="O18" s="69">
         <f t="shared" si="0"/>
-        <v>308945.13</v>
+        <v>309232.13</v>
       </c>
       <c r="P18" s="70">
         <f t="shared" si="1"/>
-        <v>318213.13</v>
+        <v>318509.13</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -3882,13 +3759,12 @@
         <v>222600.14</v>
       </c>
       <c r="H19" s="64">
-        <f>G19</f>
-        <v>222600.14</v>
+        <v>229278.14</v>
       </c>
       <c r="I19" s="65"/>
       <c r="J19" s="66">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-6678</v>
       </c>
       <c r="K19" s="66">
         <f t="shared" si="3"/>
@@ -3907,18 +3783,18 @@
       </c>
       <c r="O19" s="69">
         <f t="shared" si="0"/>
-        <v>222600.14</v>
+        <v>215922.14</v>
       </c>
       <c r="P19" s="70">
         <f t="shared" si="1"/>
-        <v>229278.14</v>
+        <v>222400.14</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -3975,7 +3851,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -3996,13 +3872,12 @@
         <v>221900.16</v>
       </c>
       <c r="H21" s="64">
-        <f>G21</f>
-        <v>221900.16</v>
+        <v>229000</v>
       </c>
       <c r="I21" s="65"/>
       <c r="J21" s="66">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-7099.8399999999965</v>
       </c>
       <c r="K21" s="66">
         <f t="shared" si="3"/>
@@ -4021,19 +3896,22 @@
       </c>
       <c r="O21" s="69">
         <f t="shared" si="0"/>
-        <v>221900.16</v>
+        <v>214800.16</v>
       </c>
       <c r="P21" s="70">
         <f t="shared" si="1"/>
-        <v>228557.16</v>
+        <v>221244.16</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
+      <c r="R21" s="182" t="s">
+        <v>172</v>
+      </c>
       <c r="S21" s="39"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4051,17 +3929,20 @@
         <v>4.55</v>
       </c>
       <c r="G22" s="64">
-        <v>318500.17</v>
-      </c>
-      <c r="H22" s="64"/>
+        <v>646396.17000000004</v>
+      </c>
+      <c r="H22" s="64">
+        <f>G22</f>
+        <v>646396.17000000004</v>
+      </c>
       <c r="I22" s="65"/>
       <c r="J22" s="66">
         <f t="shared" si="2"/>
-        <v>318500.17</v>
+        <v>0</v>
       </c>
       <c r="K22" s="66">
         <f t="shared" si="3"/>
-        <v>9395.7550150000006</v>
+        <v>0</v>
       </c>
       <c r="L22" s="67">
         <f t="shared" si="4"/>
@@ -4076,18 +3957,18 @@
       </c>
       <c r="O22" s="69">
         <f t="shared" si="0"/>
-        <v>646396.17000000004</v>
+        <v>318500.17</v>
       </c>
       <c r="P22" s="70">
         <f t="shared" si="1"/>
-        <v>665788.17000000004</v>
+        <v>328055.17</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4105,15 +3986,16 @@
         <v>3.17</v>
       </c>
       <c r="G23" s="63">
-        <v>210988.18</v>
+        <v>215570.18</v>
       </c>
       <c r="H23" s="64">
-        <v>217318.18</v>
+        <f>G23</f>
+        <v>215570.18</v>
       </c>
       <c r="I23" s="65"/>
       <c r="J23" s="66">
         <f t="shared" si="2"/>
-        <v>-6330</v>
+        <v>0</v>
       </c>
       <c r="K23" s="66">
         <f t="shared" si="3"/>
@@ -4132,18 +4014,18 @@
       </c>
       <c r="O23" s="69">
         <f t="shared" si="0"/>
-        <v>215570.18</v>
+        <v>221900.18</v>
       </c>
       <c r="P23" s="70">
         <f t="shared" si="1"/>
-        <v>222037.18</v>
+        <v>228557.18</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4161,15 +4043,16 @@
         <v>4.55</v>
       </c>
       <c r="G24" s="63">
-        <v>318500.19</v>
-      </c>
-      <c r="H24" s="143">
-        <v>328055.19</v>
+        <v>308945.19</v>
+      </c>
+      <c r="H24" s="140">
+        <f>G24</f>
+        <v>308945.19</v>
       </c>
       <c r="I24" s="65"/>
       <c r="J24" s="66">
         <f t="shared" si="2"/>
-        <v>-9555</v>
+        <v>0</v>
       </c>
       <c r="K24" s="66">
         <f t="shared" si="3"/>
@@ -4188,18 +4071,18 @@
       </c>
       <c r="O24" s="69">
         <f t="shared" si="0"/>
-        <v>308945.19</v>
+        <v>318500.19</v>
       </c>
       <c r="P24" s="70">
         <f t="shared" si="1"/>
-        <v>318213.19</v>
+        <v>328055.19</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -4217,11 +4100,11 @@
         <v>3.17</v>
       </c>
       <c r="G25" s="64">
-        <v>221900.2</v>
+        <v>226900.2</v>
       </c>
       <c r="H25" s="64">
         <f>G25</f>
-        <v>221900.2</v>
+        <v>226900.2</v>
       </c>
       <c r="I25" s="65"/>
       <c r="J25" s="66">
@@ -4241,15 +4124,15 @@
         <v>221900</v>
       </c>
       <c r="N25" s="68">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="O25" s="69">
         <f t="shared" si="0"/>
-        <v>226900.2</v>
+        <v>221900.2</v>
       </c>
       <c r="P25" s="70">
         <f t="shared" si="1"/>
-        <v>233707.2</v>
+        <v>228557.2</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="6"/>
@@ -4259,7 +4142,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -4277,11 +4160,11 @@
         <v>4.55</v>
       </c>
       <c r="G26" s="63">
-        <v>314500.21000000002</v>
+        <v>318500.21000000002</v>
       </c>
       <c r="H26" s="65">
         <f>G26</f>
-        <v>314500.21000000002</v>
+        <v>318500.21000000002</v>
       </c>
       <c r="I26" s="65"/>
       <c r="J26" s="66">
@@ -4316,7 +4199,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4334,7 +4217,7 @@
         <v>3.17</v>
       </c>
       <c r="G27" s="63">
-        <v>218960.22</v>
+        <v>58990.22</v>
       </c>
       <c r="H27" s="64">
         <f>381870.22</f>
@@ -4343,7 +4226,7 @@
       <c r="I27" s="65"/>
       <c r="J27" s="66">
         <f t="shared" si="2"/>
-        <v>-162909.99999999997</v>
+        <v>-322880</v>
       </c>
       <c r="K27" s="66">
         <f t="shared" si="3"/>
@@ -4362,18 +4245,18 @@
       </c>
       <c r="O27" s="69">
         <f t="shared" si="0"/>
-        <v>58990.22</v>
+        <v>-100979.78</v>
       </c>
       <c r="P27" s="70">
         <f t="shared" si="1"/>
-        <v>60760.22</v>
+        <v>-104008.78</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4391,15 +4274,16 @@
         <v>4.66</v>
       </c>
       <c r="G28" s="63">
-        <v>326200.23</v>
+        <v>325906.23</v>
       </c>
       <c r="H28" s="65">
-        <v>335986.23</v>
+        <f>G28</f>
+        <v>325906.23</v>
       </c>
       <c r="I28" s="65"/>
       <c r="J28" s="66">
         <f t="shared" si="2"/>
-        <v>-9786</v>
+        <v>0</v>
       </c>
       <c r="K28" s="66">
         <f t="shared" si="3"/>
@@ -4418,18 +4302,18 @@
       </c>
       <c r="O28" s="69">
         <f t="shared" si="0"/>
-        <v>316414.23</v>
+        <v>326200.23</v>
       </c>
       <c r="P28" s="70">
         <f t="shared" si="1"/>
-        <v>325906.23</v>
+        <v>335986.23</v>
       </c>
       <c r="Q28" s="40">
         <f t="shared" si="6"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4486,7 +4370,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4504,16 +4388,15 @@
         <v>4.6900000000000004</v>
       </c>
       <c r="G30" s="63">
-        <v>294034.25</v>
+        <v>328300.25</v>
       </c>
       <c r="H30" s="65">
-        <f>G30</f>
-        <v>294034.25</v>
+        <v>338149.25</v>
       </c>
       <c r="I30" s="65"/>
       <c r="J30" s="66">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9849</v>
       </c>
       <c r="K30" s="66">
         <f t="shared" si="3"/>
@@ -4532,11 +4415,11 @@
       </c>
       <c r="O30" s="69">
         <f t="shared" si="0"/>
-        <v>328300.25</v>
+        <v>318451.25</v>
       </c>
       <c r="P30" s="70">
         <f t="shared" si="1"/>
-        <v>338149.25</v>
+        <v>328005.25</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="6"/>
@@ -4546,7 +4429,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4564,11 +4447,11 @@
         <v>3.02</v>
       </c>
       <c r="G31" s="63">
-        <v>200528.26</v>
+        <v>217742.26</v>
       </c>
       <c r="H31" s="65">
         <f>G31</f>
-        <v>200528.26</v>
+        <v>217742.26</v>
       </c>
       <c r="I31" s="65"/>
       <c r="J31" s="66">
@@ -4598,16 +4481,16 @@
         <f t="shared" si="1"/>
         <v>217742.26</v>
       </c>
-      <c r="Q31" s="123">
+      <c r="Q31" s="121">
         <f t="shared" si="6"/>
         <v>0.26000000000000006</v>
       </c>
-      <c r="R31" s="130"/>
+      <c r="R31" s="128"/>
       <c r="S31" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4625,15 +4508,16 @@
         <v>0.16</v>
       </c>
       <c r="G32" s="63">
-        <v>18407.27</v>
+        <v>10648.27</v>
       </c>
       <c r="H32" s="65">
-        <v>18959.27</v>
+        <f>G32</f>
+        <v>10648.27</v>
       </c>
       <c r="I32" s="65"/>
       <c r="J32" s="66">
         <f>G32-H32</f>
-        <v>-552</v>
+        <v>0</v>
       </c>
       <c r="K32" s="66">
         <f t="shared" si="3"/>
@@ -4652,18 +4536,18 @@
       </c>
       <c r="O32" s="69">
         <f t="shared" si="0"/>
-        <v>10648.27</v>
+        <v>11200.27</v>
       </c>
       <c r="P32" s="70">
         <f t="shared" si="1"/>
-        <v>10967.27</v>
+        <v>11536.27</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="6"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4709,7 +4593,7 @@
       </c>
       <c r="Q33" s="40"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="76"/>
       <c r="C34" s="77"/>
       <c r="D34" s="78"/>
@@ -4720,11 +4604,11 @@
       </c>
       <c r="G34" s="46">
         <f>SUM(G6:G33)</f>
-        <v>9106173.7799999993</v>
+        <v>9440941.7799999993</v>
       </c>
       <c r="H34" s="54">
         <f>SUM(H6:H33)</f>
-        <v>6772536</v>
+        <v>7504571.0899999999</v>
       </c>
       <c r="I34" s="54">
         <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
@@ -4742,110 +4626,115 @@
       </c>
       <c r="N34" s="54">
         <f>SUM(N6:N33)</f>
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="O34" s="80">
         <f>SUM(O6:O32)</f>
-        <v>9419530.7799999993</v>
+        <v>9005265.7799999993</v>
       </c>
       <c r="P34" s="80">
         <f>SUM(P6:P32)</f>
-        <v>9702114.7800000012</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9275424.7799999993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="44"/>
       <c r="E35" s="44"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="148" t="s">
-        <v>182</v>
-      </c>
-      <c r="E37" s="148"/>
-      <c r="F37" s="148"/>
-      <c r="G37" s="148"/>
-      <c r="H37" s="148"/>
-      <c r="I37" s="148"/>
-      <c r="J37" s="148"/>
-      <c r="K37" s="148"/>
-      <c r="L37" s="148"/>
-      <c r="M37" s="148"/>
-      <c r="N37" s="148"/>
-      <c r="O37" s="148"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="148"/>
-      <c r="E38" s="148"/>
-      <c r="F38" s="148"/>
-      <c r="G38" s="148"/>
-      <c r="H38" s="148"/>
-      <c r="I38" s="148"/>
-      <c r="J38" s="148"/>
-      <c r="K38" s="148"/>
-      <c r="L38" s="148"/>
-      <c r="M38" s="148"/>
-      <c r="N38" s="148"/>
-      <c r="O38" s="148"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="148"/>
-      <c r="E39" s="148"/>
-      <c r="F39" s="148"/>
-      <c r="G39" s="148"/>
-      <c r="H39" s="148"/>
-      <c r="I39" s="148"/>
-      <c r="J39" s="148"/>
-      <c r="K39" s="148"/>
-      <c r="L39" s="148"/>
-      <c r="M39" s="148"/>
-      <c r="N39" s="148"/>
-      <c r="O39" s="148"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="148"/>
-      <c r="E40" s="148"/>
-      <c r="F40" s="148"/>
-      <c r="G40" s="148"/>
-      <c r="H40" s="148"/>
-      <c r="I40" s="148"/>
-      <c r="J40" s="148"/>
-      <c r="K40" s="148"/>
-      <c r="L40" s="148"/>
-      <c r="M40" s="148"/>
-      <c r="N40" s="148"/>
-      <c r="O40" s="148"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="148"/>
-      <c r="E41" s="148"/>
-      <c r="F41" s="148"/>
-      <c r="G41" s="148"/>
-      <c r="H41" s="148"/>
-      <c r="I41" s="148"/>
-      <c r="J41" s="148"/>
-      <c r="K41" s="148"/>
-      <c r="L41" s="148"/>
-      <c r="M41" s="148"/>
-      <c r="N41" s="148"/>
-      <c r="O41" s="148"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="148"/>
-      <c r="E42" s="148"/>
-      <c r="F42" s="148"/>
-      <c r="G42" s="148"/>
-      <c r="H42" s="148"/>
-      <c r="I42" s="148"/>
-      <c r="J42" s="148"/>
-      <c r="K42" s="148"/>
-      <c r="L42" s="148"/>
-      <c r="M42" s="148"/>
-      <c r="N42" s="148"/>
-      <c r="O42" s="148"/>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="159" t="s">
+        <v>153</v>
+      </c>
+      <c r="E37" s="159"/>
+      <c r="F37" s="159"/>
+      <c r="G37" s="159"/>
+      <c r="H37" s="159"/>
+      <c r="I37" s="159"/>
+      <c r="J37" s="159"/>
+      <c r="K37" s="159"/>
+      <c r="L37" s="159"/>
+      <c r="M37" s="159"/>
+      <c r="N37" s="159"/>
+      <c r="O37" s="159"/>
+    </row>
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="159"/>
+      <c r="E38" s="159"/>
+      <c r="F38" s="159"/>
+      <c r="G38" s="159"/>
+      <c r="H38" s="159"/>
+      <c r="I38" s="159"/>
+      <c r="J38" s="159"/>
+      <c r="K38" s="159"/>
+      <c r="L38" s="159"/>
+      <c r="M38" s="159"/>
+      <c r="N38" s="159"/>
+      <c r="O38" s="159"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="159"/>
+      <c r="E39" s="159"/>
+      <c r="F39" s="159"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="159"/>
+      <c r="I39" s="159"/>
+      <c r="J39" s="159"/>
+      <c r="K39" s="159"/>
+      <c r="L39" s="159"/>
+      <c r="M39" s="159"/>
+      <c r="N39" s="159"/>
+      <c r="O39" s="159"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="159"/>
+      <c r="E40" s="159"/>
+      <c r="F40" s="159"/>
+      <c r="G40" s="159"/>
+      <c r="H40" s="159"/>
+      <c r="I40" s="159"/>
+      <c r="J40" s="159"/>
+      <c r="K40" s="159"/>
+      <c r="L40" s="159"/>
+      <c r="M40" s="159"/>
+      <c r="N40" s="159"/>
+      <c r="O40" s="159"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="159"/>
+      <c r="E41" s="159"/>
+      <c r="F41" s="159"/>
+      <c r="G41" s="159"/>
+      <c r="H41" s="159"/>
+      <c r="I41" s="159"/>
+      <c r="J41" s="159"/>
+      <c r="K41" s="159"/>
+      <c r="L41" s="159"/>
+      <c r="M41" s="159"/>
+      <c r="N41" s="159"/>
+      <c r="O41" s="159"/>
+    </row>
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="159"/>
+      <c r="E42" s="159"/>
+      <c r="F42" s="159"/>
+      <c r="G42" s="159"/>
+      <c r="H42" s="159"/>
+      <c r="I42" s="159"/>
+      <c r="J42" s="159"/>
+      <c r="K42" s="159"/>
+      <c r="L42" s="159"/>
+      <c r="M42" s="159"/>
+      <c r="N42" s="159"/>
+      <c r="O42" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4858,11 +4747,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/colombres/Octubre/Octubre COLOMBRES 360.xlsx
+++ b/colombres/Octubre/Octubre COLOMBRES 360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9577E97E-3A1F-4267-A8E8-AE889B01F6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAD42BC-9C20-4C68-9BBC-FAB39C044C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1188,7 +1188,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1394,116 +1394,115 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1896,68 +1895,68 @@
       <c r="D3" s="119"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="150" t="s">
+      <c r="A4" s="162" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="150"/>
+      <c r="B4" s="162"/>
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="150"/>
-      <c r="B5" s="150"/>
+      <c r="A5" s="162"/>
+      <c r="B5" s="162"/>
       <c r="C5" s="120"/>
       <c r="D5" s="120"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="150"/>
-      <c r="B6" s="150"/>
+      <c r="A6" s="162"/>
+      <c r="B6" s="162"/>
       <c r="C6" s="120"/>
       <c r="D6" s="120"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="150"/>
-      <c r="B7" s="150"/>
+      <c r="A7" s="162"/>
+      <c r="B7" s="162"/>
       <c r="C7" s="120"/>
       <c r="D7" s="120"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="147" t="s">
+      <c r="B9" s="161" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="147"/>
+      <c r="B10" s="161"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="147"/>
+      <c r="B11" s="161"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="151" t="s">
+      <c r="A14" s="163" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="151"/>
-      <c r="C14" s="151"/>
-      <c r="D14" s="151"/>
+      <c r="B14" s="163"/>
+      <c r="C14" s="163"/>
+      <c r="D14" s="163"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="151"/>
-      <c r="B15" s="151"/>
-      <c r="C15" s="151"/>
-      <c r="D15" s="151"/>
+      <c r="A15" s="163"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="163"/>
+      <c r="D15" s="163"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="151"/>
-      <c r="B16" s="151"/>
-      <c r="C16" s="151"/>
-      <c r="D16" s="151"/>
+      <c r="A16" s="163"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="163"/>
+      <c r="D16" s="163"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="151"/>
-      <c r="B17" s="151"/>
-      <c r="C17" s="151"/>
-      <c r="D17" s="151"/>
+      <c r="A17" s="163"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="163"/>
+      <c r="D17" s="163"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2031,10 +2030,10 @@
         <v>992466.6399999999</v>
       </c>
       <c r="D27" s="84"/>
-      <c r="F27" s="145" t="s">
+      <c r="F27" s="159" t="s">
         <v>148</v>
       </c>
-      <c r="G27" s="146"/>
+      <c r="G27" s="160"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="125" t="s">
@@ -2047,8 +2046,8 @@
         <v>971916.1</v>
       </c>
       <c r="D28" s="83"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="146"/>
+      <c r="F28" s="159"/>
+      <c r="G28" s="160"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -2174,7 +2173,7 @@
         <f>35000*3</f>
         <v>105000</v>
       </c>
-      <c r="D40" s="180" t="s">
+      <c r="D40" s="145" t="s">
         <v>159</v>
       </c>
       <c r="G40" s="14"/>
@@ -2187,7 +2186,7 @@
         <v>166</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="180"/>
+      <c r="D41" s="145"/>
       <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2210,10 +2209,10 @@
       <c r="D43" s="60"/>
     </row>
     <row r="44" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="148" t="s">
+      <c r="A44" s="150" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="149"/>
+      <c r="B44" s="151"/>
       <c r="C44" s="142">
         <v>175052</v>
       </c>
@@ -2222,10 +2221,10 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="148" t="s">
+      <c r="A45" s="150" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="149"/>
+      <c r="B45" s="151"/>
       <c r="C45" s="143">
         <v>4203</v>
       </c>
@@ -2424,24 +2423,24 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="148" t="s">
+      <c r="A63" s="150" t="s">
         <v>168</v>
       </c>
-      <c r="B63" s="149"/>
+      <c r="B63" s="151"/>
       <c r="C63" s="141">
         <v>15000</v>
       </c>
-      <c r="D63" s="181"/>
+      <c r="D63" s="146"/>
     </row>
     <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="148" t="s">
+      <c r="A64" s="150" t="s">
         <v>169</v>
       </c>
-      <c r="B64" s="149"/>
+      <c r="B64" s="151"/>
       <c r="C64" s="141">
         <v>175000</v>
       </c>
-      <c r="D64" s="181"/>
+      <c r="D64" s="146"/>
     </row>
     <row r="65" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="155" t="s">
@@ -2462,8 +2461,8 @@
       <c r="B66" s="27"/>
       <c r="C66" s="25"/>
       <c r="D66" s="94">
-        <f>SUM(C62:C62)</f>
-        <v>11200</v>
+        <f>SUM(C62:C65)</f>
+        <v>269150</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2518,8 +2517,8 @@
       <c r="B72" s="153"/>
       <c r="C72" s="154"/>
       <c r="D72" s="98">
-        <f>7000000-6763271.11</f>
-        <v>236728.88999999966</v>
+        <f>8500000-6763271.11-257950</f>
+        <v>1478778.8899999997</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2536,7 +2535,7 @@
       <c r="C74" s="101"/>
       <c r="D74" s="102">
         <f>(SUM(D29:D72))</f>
-        <v>7000000</v>
+        <v>8500000</v>
       </c>
       <c r="E74" s="40"/>
     </row>
@@ -2558,14 +2557,14 @@
       <c r="D77" s="104"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="148"/>
-      <c r="B78" s="149"/>
+      <c r="A78" s="150"/>
+      <c r="B78" s="151"/>
       <c r="C78" s="91"/>
       <c r="D78" s="89"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="148"/>
-      <c r="B79" s="149"/>
+      <c r="A79" s="150"/>
+      <c r="B79" s="151"/>
       <c r="C79" s="91"/>
       <c r="D79" s="89"/>
     </row>
@@ -2613,7 +2612,7 @@
       </c>
       <c r="B88" s="82">
         <f>D74</f>
-        <v>7000000</v>
+        <v>8500000</v>
       </c>
       <c r="C88" s="40"/>
     </row>
@@ -2623,7 +2622,7 @@
       </c>
       <c r="B89" s="82">
         <f>D74-D72</f>
-        <v>6763271.1100000003</v>
+        <v>7021221.1100000003</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2647,22 +2646,22 @@
     <row r="92" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="161"/>
-      <c r="B94" s="161"/>
-      <c r="C94" s="161"/>
-      <c r="D94" s="161"/>
+      <c r="A94" s="149"/>
+      <c r="B94" s="149"/>
+      <c r="C94" s="149"/>
+      <c r="D94" s="149"/>
     </row>
     <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="161"/>
-      <c r="B95" s="161"/>
-      <c r="C95" s="161"/>
-      <c r="D95" s="161"/>
+      <c r="A95" s="149"/>
+      <c r="B95" s="149"/>
+      <c r="C95" s="149"/>
+      <c r="D95" s="149"/>
     </row>
     <row r="96" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="161"/>
-      <c r="B96" s="161"/>
-      <c r="C96" s="161"/>
-      <c r="D96" s="161"/>
+      <c r="A96" s="149"/>
+      <c r="B96" s="149"/>
+      <c r="C96" s="149"/>
+      <c r="D96" s="149"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
@@ -2710,7 +2709,7 @@
       </c>
       <c r="B103" s="93">
         <f>-B89</f>
-        <v>-6763271.1100000003</v>
+        <v>-7021221.1100000003</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2728,7 +2727,7 @@
       </c>
       <c r="B105" s="112">
         <f>SUM(B99:B104)</f>
-        <v>3963290.9299999988</v>
+        <v>3705340.9299999988</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2736,14 +2735,14 @@
       <c r="C106" s="40"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="160" t="s">
+      <c r="A108" s="148" t="s">
         <v>78</v>
       </c>
-      <c r="B108" s="160"/>
+      <c r="B108" s="148"/>
     </row>
     <row r="109" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="160"/>
-      <c r="B109" s="160"/>
+      <c r="A109" s="148"/>
+      <c r="B109" s="148"/>
     </row>
     <row r="110" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="105"/>
@@ -2782,47 +2781,47 @@
       <c r="L117" s="8"/>
     </row>
     <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="159"/>
-      <c r="B118" s="159"/>
-      <c r="C118" s="159"/>
-      <c r="D118" s="159"/>
+      <c r="A118" s="147"/>
+      <c r="B118" s="147"/>
+      <c r="C118" s="147"/>
+      <c r="D118" s="147"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="159"/>
-      <c r="B119" s="159"/>
-      <c r="C119" s="159"/>
-      <c r="D119" s="159"/>
+      <c r="A119" s="147"/>
+      <c r="B119" s="147"/>
+      <c r="C119" s="147"/>
+      <c r="D119" s="147"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="159"/>
-      <c r="B120" s="159"/>
-      <c r="C120" s="159"/>
-      <c r="D120" s="159"/>
+      <c r="A120" s="147"/>
+      <c r="B120" s="147"/>
+      <c r="C120" s="147"/>
+      <c r="D120" s="147"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="159"/>
-      <c r="B121" s="159"/>
-      <c r="C121" s="159"/>
-      <c r="D121" s="159"/>
+      <c r="A121" s="147"/>
+      <c r="B121" s="147"/>
+      <c r="C121" s="147"/>
+      <c r="D121" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A118:D121"/>
-    <mergeCell ref="A108:B109"/>
-    <mergeCell ref="A94:D96"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
     <mergeCell ref="F27:G28"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A118:D121"/>
+    <mergeCell ref="A108:B109"/>
+    <mergeCell ref="A94:D96"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2858,18 +2857,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="162" t="s">
+      <c r="B1" s="170" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2878,39 +2877,39 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="162"/>
-      <c r="C2" s="162"/>
-      <c r="D2" s="162"/>
-      <c r="E2" s="162"/>
-      <c r="F2" s="162"/>
-      <c r="G2" s="162"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="162"/>
-      <c r="J2" s="162"/>
-      <c r="K2" s="162"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="130">
-        <v>7000000</v>
+        <v>8500000</v>
       </c>
       <c r="P2" s="47"/>
       <c r="Q2" s="14"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="163"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2920,76 +2919,76 @@
       <c r="P3" s="52"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="176" t="s">
+      <c r="A4" s="164" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="178" t="s">
+      <c r="B4" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="166" t="s">
+      <c r="C4" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="166" t="s">
+      <c r="E4" s="168" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="166" t="s">
+      <c r="F4" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="166" t="s">
+      <c r="G4" s="168" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="166" t="s">
+      <c r="H4" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="166" t="s">
+      <c r="I4" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="171" t="s">
+      <c r="J4" s="177" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="168" t="s">
+      <c r="K4" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="168" t="s">
+      <c r="L4" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="168" t="s">
+      <c r="M4" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="174" t="s">
+      <c r="N4" s="180" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="164" t="s">
+      <c r="P4" s="172" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="40"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="177"/>
-      <c r="B5" s="179"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="170"/>
-      <c r="I5" s="167"/>
-      <c r="J5" s="172"/>
-      <c r="K5" s="169"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="169"/>
-      <c r="N5" s="175"/>
+      <c r="A5" s="165"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
+      <c r="I5" s="174"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="179"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="181"/>
       <c r="O5" s="53" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/11</v>
       </c>
-      <c r="P5" s="165"/>
+      <c r="P5" s="173"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3029,18 +3028,18 @@
       </c>
       <c r="M6" s="67">
         <f>O$2*F6%</f>
-        <v>319900.00000000006</v>
+        <v>388450.00000000006</v>
       </c>
       <c r="N6" s="68">
         <v>0</v>
       </c>
       <c r="O6" s="69">
         <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>329989.01</v>
+        <v>398539.01</v>
       </c>
       <c r="P6" s="70">
         <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
-        <v>339889.01</v>
+        <v>410495.01</v>
       </c>
       <c r="Q6" s="40">
         <v>0.01</v>
@@ -3084,18 +3083,18 @@
       </c>
       <c r="M7" s="67">
         <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
-        <v>214900</v>
+        <v>260949.99999999997</v>
       </c>
       <c r="N7" s="68">
         <v>0</v>
       </c>
       <c r="O7" s="69">
         <f t="shared" si="0"/>
-        <v>447965.02</v>
+        <v>494015.02</v>
       </c>
       <c r="P7" s="70">
         <f t="shared" si="1"/>
-        <v>461404.02</v>
+        <v>508835.02</v>
       </c>
       <c r="Q7" s="40">
         <f>Q6+0.01</f>
@@ -3143,18 +3142,18 @@
       </c>
       <c r="M8" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N8" s="68">
         <v>0</v>
       </c>
       <c r="O8" s="69">
         <f t="shared" si="0"/>
-        <v>2248136.0299999998</v>
+        <v>2316386.0299999998</v>
       </c>
       <c r="P8" s="70">
         <f t="shared" si="1"/>
-        <v>2315580.0299999998</v>
+        <v>2385878.0299999998</v>
       </c>
       <c r="Q8" s="40">
         <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
@@ -3199,18 +3198,18 @@
       </c>
       <c r="M9" s="67">
         <f t="shared" si="5"/>
-        <v>213500</v>
+        <v>259250</v>
       </c>
       <c r="N9" s="68">
         <v>0</v>
       </c>
       <c r="O9" s="69">
         <f t="shared" si="0"/>
-        <v>184979.04</v>
+        <v>230729.04</v>
       </c>
       <c r="P9" s="70">
         <f t="shared" si="1"/>
-        <v>190528.04</v>
+        <v>237651.04</v>
       </c>
       <c r="Q9" s="40">
         <f t="shared" si="6"/>
@@ -3260,18 +3259,18 @@
       </c>
       <c r="M10" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N10" s="68">
         <v>0</v>
       </c>
       <c r="O10" s="69">
         <f t="shared" si="0"/>
-        <v>318348.05</v>
+        <v>386598.05</v>
       </c>
       <c r="P10" s="70">
         <f t="shared" si="1"/>
-        <v>327898.05</v>
+        <v>398196.05</v>
       </c>
       <c r="Q10" s="40">
         <f t="shared" si="6"/>
@@ -3317,18 +3316,18 @@
       </c>
       <c r="M11" s="67">
         <f t="shared" si="5"/>
-        <v>213500</v>
+        <v>259250</v>
       </c>
       <c r="N11" s="68">
         <v>0</v>
       </c>
       <c r="O11" s="69">
         <f t="shared" si="0"/>
-        <v>207095.06</v>
+        <v>252845.06</v>
       </c>
       <c r="P11" s="70">
         <f t="shared" si="1"/>
-        <v>213308.06</v>
+        <v>260430.06</v>
       </c>
       <c r="Q11" s="40">
         <f t="shared" si="6"/>
@@ -3373,18 +3372,18 @@
       </c>
       <c r="M12" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N12" s="68">
         <v>0</v>
       </c>
       <c r="O12" s="69">
         <f t="shared" si="0"/>
-        <v>317000.07</v>
+        <v>385250.07</v>
       </c>
       <c r="P12" s="70">
         <f t="shared" si="1"/>
-        <v>326510.07</v>
+        <v>396808.07</v>
       </c>
       <c r="Q12" s="40">
         <f t="shared" si="6"/>
@@ -3431,18 +3430,18 @@
       </c>
       <c r="M13" s="67">
         <f t="shared" si="5"/>
-        <v>213500</v>
+        <v>259250</v>
       </c>
       <c r="N13" s="68">
         <v>0</v>
       </c>
       <c r="O13" s="69">
         <f t="shared" si="0"/>
-        <v>207695.08</v>
+        <v>253445.08</v>
       </c>
       <c r="P13" s="70">
         <f t="shared" si="1"/>
-        <v>213926.08</v>
+        <v>261048.08</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" si="6"/>
@@ -3488,18 +3487,18 @@
       </c>
       <c r="M14" s="67">
         <f t="shared" si="5"/>
-        <v>319199.99999999994</v>
+        <v>387599.99999999994</v>
       </c>
       <c r="N14" s="68">
         <v>0</v>
       </c>
       <c r="O14" s="69">
         <f t="shared" si="0"/>
-        <v>318400.09000000003</v>
+        <v>386800.09</v>
       </c>
       <c r="P14" s="70">
         <f t="shared" si="1"/>
-        <v>327952.09000000003</v>
+        <v>398404.09</v>
       </c>
       <c r="Q14" s="40">
         <f t="shared" si="6"/>
@@ -3547,18 +3546,18 @@
       </c>
       <c r="M15" s="67">
         <f t="shared" si="5"/>
-        <v>213500</v>
+        <v>259250</v>
       </c>
       <c r="N15" s="68">
         <v>0</v>
       </c>
       <c r="O15" s="69">
         <f t="shared" si="0"/>
-        <v>444930.1</v>
+        <v>490680.1</v>
       </c>
       <c r="P15" s="70">
         <f t="shared" si="1"/>
-        <v>458278.1</v>
+        <v>505400.1</v>
       </c>
       <c r="Q15" s="40">
         <f t="shared" si="6"/>
@@ -3607,18 +3606,18 @@
       </c>
       <c r="M16" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N16" s="68">
         <v>0</v>
       </c>
       <c r="O16" s="69">
         <f t="shared" si="0"/>
-        <v>318500.11</v>
+        <v>386750.11</v>
       </c>
       <c r="P16" s="70">
         <f t="shared" si="1"/>
-        <v>328055.11</v>
+        <v>398353.11</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" si="6"/>
@@ -3664,18 +3663,18 @@
       </c>
       <c r="M17" s="67">
         <f t="shared" si="5"/>
-        <v>213500</v>
+        <v>259250</v>
       </c>
       <c r="N17" s="68">
         <v>0</v>
       </c>
       <c r="O17" s="69">
         <f t="shared" si="0"/>
-        <v>213500.12</v>
+        <v>259250.12</v>
       </c>
       <c r="P17" s="70">
         <f t="shared" si="1"/>
-        <v>219905.12</v>
+        <v>267028.12</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="6"/>
@@ -3720,18 +3719,18 @@
       </c>
       <c r="M18" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N18" s="68">
         <v>0</v>
       </c>
       <c r="O18" s="69">
         <f t="shared" si="0"/>
-        <v>309232.13</v>
+        <v>377482.13</v>
       </c>
       <c r="P18" s="70">
         <f t="shared" si="1"/>
-        <v>318509.13</v>
+        <v>388806.13</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="6"/>
@@ -3776,18 +3775,18 @@
       </c>
       <c r="M19" s="67">
         <f t="shared" si="5"/>
-        <v>222600</v>
+        <v>270300</v>
       </c>
       <c r="N19" s="68">
         <v>0</v>
       </c>
       <c r="O19" s="69">
         <f t="shared" si="0"/>
-        <v>215922.14</v>
+        <v>263622.14</v>
       </c>
       <c r="P19" s="70">
         <f t="shared" si="1"/>
-        <v>222400.14</v>
+        <v>271531.14</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="6"/>
@@ -3833,18 +3832,18 @@
       </c>
       <c r="M20" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N20" s="68">
         <v>0</v>
       </c>
       <c r="O20" s="69">
         <f t="shared" si="0"/>
-        <v>318500.15000000002</v>
+        <v>386750.15</v>
       </c>
       <c r="P20" s="70">
         <f t="shared" si="1"/>
-        <v>328055.15000000002</v>
+        <v>398353.15</v>
       </c>
       <c r="Q20" s="40">
         <f t="shared" si="6"/>
@@ -3889,24 +3888,24 @@
       </c>
       <c r="M21" s="67">
         <f t="shared" si="5"/>
-        <v>221900</v>
+        <v>269450</v>
       </c>
       <c r="N21" s="68">
         <v>0</v>
       </c>
       <c r="O21" s="69">
         <f t="shared" si="0"/>
-        <v>214800.16</v>
+        <v>262350.15999999997</v>
       </c>
       <c r="P21" s="70">
         <f t="shared" si="1"/>
-        <v>221244.16</v>
+        <v>270221.15999999997</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
-      <c r="R21" s="182" t="s">
+      <c r="R21" t="s">
         <v>172</v>
       </c>
       <c r="S21" s="39"/>
@@ -3950,18 +3949,18 @@
       </c>
       <c r="M22" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N22" s="68">
         <v>0</v>
       </c>
       <c r="O22" s="69">
         <f t="shared" si="0"/>
-        <v>318500.17</v>
+        <v>386750.17</v>
       </c>
       <c r="P22" s="70">
         <f t="shared" si="1"/>
-        <v>328055.17</v>
+        <v>398353.17</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="6"/>
@@ -4007,18 +4006,18 @@
       </c>
       <c r="M23" s="67">
         <f t="shared" si="5"/>
-        <v>221900</v>
+        <v>269450</v>
       </c>
       <c r="N23" s="68">
         <v>0</v>
       </c>
       <c r="O23" s="69">
         <f t="shared" si="0"/>
-        <v>221900.18</v>
+        <v>269450.18</v>
       </c>
       <c r="P23" s="70">
         <f t="shared" si="1"/>
-        <v>228557.18</v>
+        <v>277534.18</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="6"/>
@@ -4064,18 +4063,18 @@
       </c>
       <c r="M24" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N24" s="68">
         <v>0</v>
       </c>
       <c r="O24" s="69">
         <f t="shared" si="0"/>
-        <v>318500.19</v>
+        <v>386750.19</v>
       </c>
       <c r="P24" s="70">
         <f t="shared" si="1"/>
-        <v>328055.19</v>
+        <v>398353.19</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" si="6"/>
@@ -4121,18 +4120,18 @@
       </c>
       <c r="M25" s="67">
         <f t="shared" si="5"/>
-        <v>221900</v>
+        <v>269450</v>
       </c>
       <c r="N25" s="68">
         <v>0</v>
       </c>
       <c r="O25" s="69">
         <f t="shared" si="0"/>
-        <v>221900.2</v>
+        <v>269450.2</v>
       </c>
       <c r="P25" s="70">
         <f t="shared" si="1"/>
-        <v>228557.2</v>
+        <v>277534.2</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="6"/>
@@ -4181,18 +4180,18 @@
       </c>
       <c r="M26" s="67">
         <f t="shared" si="5"/>
-        <v>318500</v>
+        <v>386750</v>
       </c>
       <c r="N26" s="68">
         <v>0</v>
       </c>
       <c r="O26" s="69">
         <f t="shared" si="0"/>
-        <v>318500.21000000002</v>
+        <v>386750.21</v>
       </c>
       <c r="P26" s="70">
         <f t="shared" si="1"/>
-        <v>328055.21000000002</v>
+        <v>398353.21</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="6"/>
@@ -4238,18 +4237,18 @@
       </c>
       <c r="M27" s="67">
         <f t="shared" si="5"/>
-        <v>221900</v>
+        <v>269450</v>
       </c>
       <c r="N27" s="68">
         <v>0</v>
       </c>
       <c r="O27" s="69">
         <f t="shared" si="0"/>
-        <v>-100979.78</v>
+        <v>-53429.78</v>
       </c>
       <c r="P27" s="70">
         <f t="shared" si="1"/>
-        <v>-104008.78</v>
+        <v>-55032.78</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="6"/>
@@ -4295,18 +4294,18 @@
       </c>
       <c r="M28" s="67">
         <f t="shared" si="5"/>
-        <v>326200</v>
+        <v>396100</v>
       </c>
       <c r="N28" s="68">
         <v>0</v>
       </c>
       <c r="O28" s="69">
         <f t="shared" si="0"/>
-        <v>326200.23</v>
+        <v>396100.23</v>
       </c>
       <c r="P28" s="70">
         <f t="shared" si="1"/>
-        <v>335986.23</v>
+        <v>407983.23</v>
       </c>
       <c r="Q28" s="40">
         <f t="shared" si="6"/>
@@ -4352,18 +4351,18 @@
       </c>
       <c r="M29" s="67">
         <f t="shared" si="5"/>
-        <v>224699.99999999997</v>
+        <v>272850</v>
       </c>
       <c r="N29" s="68">
         <v>0</v>
       </c>
       <c r="O29" s="69">
         <f t="shared" si="0"/>
-        <v>224700.24</v>
+        <v>272850.24</v>
       </c>
       <c r="P29" s="70">
         <f t="shared" si="1"/>
-        <v>231441.24</v>
+        <v>281036.24</v>
       </c>
       <c r="Q29" s="40">
         <f t="shared" si="6"/>
@@ -4408,18 +4407,18 @@
       </c>
       <c r="M30" s="67">
         <f t="shared" si="5"/>
-        <v>328300.00000000006</v>
+        <v>398650.00000000006</v>
       </c>
       <c r="N30" s="68">
         <v>0</v>
       </c>
       <c r="O30" s="69">
         <f t="shared" si="0"/>
-        <v>318451.25</v>
+        <v>388801.25</v>
       </c>
       <c r="P30" s="70">
         <f t="shared" si="1"/>
-        <v>328005.25</v>
+        <v>400465.25</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="6"/>
@@ -4468,18 +4467,18 @@
       </c>
       <c r="M31" s="67">
         <f t="shared" si="5"/>
-        <v>211400</v>
+        <v>256700</v>
       </c>
       <c r="N31" s="68">
         <v>0</v>
       </c>
       <c r="O31" s="69">
         <f t="shared" si="0"/>
-        <v>211400.26</v>
+        <v>256700.26</v>
       </c>
       <c r="P31" s="70">
         <f t="shared" si="1"/>
-        <v>217742.26</v>
+        <v>264401.26</v>
       </c>
       <c r="Q31" s="121">
         <f t="shared" si="6"/>
@@ -4529,18 +4528,18 @@
       </c>
       <c r="M32" s="67">
         <f>O$2*F32%</f>
-        <v>11200</v>
+        <v>13600</v>
       </c>
       <c r="N32" s="68">
         <v>0</v>
       </c>
       <c r="O32" s="69">
         <f t="shared" si="0"/>
-        <v>11200.27</v>
+        <v>13600.27</v>
       </c>
       <c r="P32" s="70">
         <f t="shared" si="1"/>
-        <v>11536.27</v>
+        <v>14008.27</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="6"/>
@@ -4622,7 +4621,7 @@
       </c>
       <c r="M34" s="54">
         <f>SUM(M6:M33)</f>
-        <v>7000000</v>
+        <v>8500000</v>
       </c>
       <c r="N34" s="54">
         <f>SUM(N6:N33)</f>
@@ -4630,11 +4629,11 @@
       </c>
       <c r="O34" s="80">
         <f>SUM(O6:O32)</f>
-        <v>9005265.7799999993</v>
+        <v>10505265.779999999</v>
       </c>
       <c r="P34" s="80">
         <f>SUM(P6:P32)</f>
-        <v>9275424.7799999993</v>
+        <v>10820427.779999999</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4643,98 +4642,93 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="159" t="s">
+      <c r="D37" s="147" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="159"/>
-      <c r="F37" s="159"/>
-      <c r="G37" s="159"/>
-      <c r="H37" s="159"/>
-      <c r="I37" s="159"/>
-      <c r="J37" s="159"/>
-      <c r="K37" s="159"/>
-      <c r="L37" s="159"/>
-      <c r="M37" s="159"/>
-      <c r="N37" s="159"/>
-      <c r="O37" s="159"/>
+      <c r="E37" s="147"/>
+      <c r="F37" s="147"/>
+      <c r="G37" s="147"/>
+      <c r="H37" s="147"/>
+      <c r="I37" s="147"/>
+      <c r="J37" s="147"/>
+      <c r="K37" s="147"/>
+      <c r="L37" s="147"/>
+      <c r="M37" s="147"/>
+      <c r="N37" s="147"/>
+      <c r="O37" s="147"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="159"/>
-      <c r="E38" s="159"/>
-      <c r="F38" s="159"/>
-      <c r="G38" s="159"/>
-      <c r="H38" s="159"/>
-      <c r="I38" s="159"/>
-      <c r="J38" s="159"/>
-      <c r="K38" s="159"/>
-      <c r="L38" s="159"/>
-      <c r="M38" s="159"/>
-      <c r="N38" s="159"/>
-      <c r="O38" s="159"/>
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="147"/>
+      <c r="N38" s="147"/>
+      <c r="O38" s="147"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="159"/>
-      <c r="E39" s="159"/>
-      <c r="F39" s="159"/>
-      <c r="G39" s="159"/>
-      <c r="H39" s="159"/>
-      <c r="I39" s="159"/>
-      <c r="J39" s="159"/>
-      <c r="K39" s="159"/>
-      <c r="L39" s="159"/>
-      <c r="M39" s="159"/>
-      <c r="N39" s="159"/>
-      <c r="O39" s="159"/>
+      <c r="D39" s="147"/>
+      <c r="E39" s="147"/>
+      <c r="F39" s="147"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="147"/>
+      <c r="J39" s="147"/>
+      <c r="K39" s="147"/>
+      <c r="L39" s="147"/>
+      <c r="M39" s="147"/>
+      <c r="N39" s="147"/>
+      <c r="O39" s="147"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="159"/>
-      <c r="E40" s="159"/>
-      <c r="F40" s="159"/>
-      <c r="G40" s="159"/>
-      <c r="H40" s="159"/>
-      <c r="I40" s="159"/>
-      <c r="J40" s="159"/>
-      <c r="K40" s="159"/>
-      <c r="L40" s="159"/>
-      <c r="M40" s="159"/>
-      <c r="N40" s="159"/>
-      <c r="O40" s="159"/>
+      <c r="D40" s="147"/>
+      <c r="E40" s="147"/>
+      <c r="F40" s="147"/>
+      <c r="G40" s="147"/>
+      <c r="H40" s="147"/>
+      <c r="I40" s="147"/>
+      <c r="J40" s="147"/>
+      <c r="K40" s="147"/>
+      <c r="L40" s="147"/>
+      <c r="M40" s="147"/>
+      <c r="N40" s="147"/>
+      <c r="O40" s="147"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="159"/>
-      <c r="E41" s="159"/>
-      <c r="F41" s="159"/>
-      <c r="G41" s="159"/>
-      <c r="H41" s="159"/>
-      <c r="I41" s="159"/>
-      <c r="J41" s="159"/>
-      <c r="K41" s="159"/>
-      <c r="L41" s="159"/>
-      <c r="M41" s="159"/>
-      <c r="N41" s="159"/>
-      <c r="O41" s="159"/>
+      <c r="D41" s="147"/>
+      <c r="E41" s="147"/>
+      <c r="F41" s="147"/>
+      <c r="G41" s="147"/>
+      <c r="H41" s="147"/>
+      <c r="I41" s="147"/>
+      <c r="J41" s="147"/>
+      <c r="K41" s="147"/>
+      <c r="L41" s="147"/>
+      <c r="M41" s="147"/>
+      <c r="N41" s="147"/>
+      <c r="O41" s="147"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="159"/>
-      <c r="E42" s="159"/>
-      <c r="F42" s="159"/>
-      <c r="G42" s="159"/>
-      <c r="H42" s="159"/>
-      <c r="I42" s="159"/>
-      <c r="J42" s="159"/>
-      <c r="K42" s="159"/>
-      <c r="L42" s="159"/>
-      <c r="M42" s="159"/>
-      <c r="N42" s="159"/>
-      <c r="O42" s="159"/>
+      <c r="D42" s="147"/>
+      <c r="E42" s="147"/>
+      <c r="F42" s="147"/>
+      <c r="G42" s="147"/>
+      <c r="H42" s="147"/>
+      <c r="I42" s="147"/>
+      <c r="J42" s="147"/>
+      <c r="K42" s="147"/>
+      <c r="L42" s="147"/>
+      <c r="M42" s="147"/>
+      <c r="N42" s="147"/>
+      <c r="O42" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4747,6 +4741,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/colombres/Octubre/Octubre COLOMBRES 360.xlsx
+++ b/colombres/Octubre/Octubre COLOMBRES 360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAD42BC-9C20-4C68-9BBC-FAB39C044C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB0F7F9-75AF-4A10-ABA8-056D216C4DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1398,6 +1398,48 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1407,46 +1449,46 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1460,48 +1502,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1895,68 +1895,68 @@
       <c r="D3" s="119"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="162" t="s">
+      <c r="A4" s="152" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="162"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="162"/>
-      <c r="B5" s="162"/>
+      <c r="A5" s="152"/>
+      <c r="B5" s="152"/>
       <c r="C5" s="120"/>
       <c r="D5" s="120"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="162"/>
-      <c r="B6" s="162"/>
+      <c r="A6" s="152"/>
+      <c r="B6" s="152"/>
       <c r="C6" s="120"/>
       <c r="D6" s="120"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="162"/>
-      <c r="B7" s="162"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="152"/>
       <c r="C7" s="120"/>
       <c r="D7" s="120"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="161" t="s">
+      <c r="B9" s="149" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="161"/>
+      <c r="B10" s="149"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="161"/>
+      <c r="B11" s="149"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="163" t="s">
+      <c r="A14" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="163"/>
-      <c r="C14" s="163"/>
-      <c r="D14" s="163"/>
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="163"/>
-      <c r="B15" s="163"/>
-      <c r="C15" s="163"/>
-      <c r="D15" s="163"/>
+      <c r="A15" s="153"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="163"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="163"/>
-      <c r="D16" s="163"/>
+      <c r="A16" s="153"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="163"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="163"/>
-      <c r="D17" s="163"/>
+      <c r="A17" s="153"/>
+      <c r="B17" s="153"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2030,10 +2030,10 @@
         <v>992466.6399999999</v>
       </c>
       <c r="D27" s="84"/>
-      <c r="F27" s="159" t="s">
+      <c r="F27" s="147" t="s">
         <v>148</v>
       </c>
-      <c r="G27" s="160"/>
+      <c r="G27" s="148"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="125" t="s">
@@ -2046,8 +2046,8 @@
         <v>971916.1</v>
       </c>
       <c r="D28" s="83"/>
-      <c r="F28" s="159"/>
-      <c r="G28" s="160"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="148"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -2366,10 +2366,10 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="157" t="s">
+      <c r="A57" s="159" t="s">
         <v>167</v>
       </c>
-      <c r="B57" s="158"/>
+      <c r="B57" s="160"/>
       <c r="C57" s="141"/>
       <c r="D57" s="122"/>
     </row>
@@ -2443,10 +2443,10 @@
       <c r="D64" s="146"/>
     </row>
     <row r="65" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="155" t="s">
+      <c r="A65" s="157" t="s">
         <v>155</v>
       </c>
-      <c r="B65" s="156"/>
+      <c r="B65" s="158"/>
       <c r="C65" s="144">
         <v>67950</v>
       </c>
@@ -2511,14 +2511,14 @@
       <c r="D71" s="97"/>
     </row>
     <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="152" t="s">
+      <c r="A72" s="154" t="s">
         <v>147</v>
       </c>
-      <c r="B72" s="153"/>
-      <c r="C72" s="154"/>
+      <c r="B72" s="155"/>
+      <c r="C72" s="156"/>
       <c r="D72" s="98">
-        <f>8500000-6763271.11-257950</f>
-        <v>1478778.8899999997</v>
+        <f>9000000-6763271.11-257950</f>
+        <v>1978778.8899999997</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2535,7 +2535,7 @@
       <c r="C74" s="101"/>
       <c r="D74" s="102">
         <f>(SUM(D29:D72))</f>
-        <v>8500000</v>
+        <v>9000000</v>
       </c>
       <c r="E74" s="40"/>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B88" s="82">
         <f>D74</f>
-        <v>8500000</v>
+        <v>9000000</v>
       </c>
       <c r="C88" s="40"/>
     </row>
@@ -2646,22 +2646,22 @@
     <row r="92" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="149"/>
-      <c r="B94" s="149"/>
-      <c r="C94" s="149"/>
-      <c r="D94" s="149"/>
+      <c r="A94" s="163"/>
+      <c r="B94" s="163"/>
+      <c r="C94" s="163"/>
+      <c r="D94" s="163"/>
     </row>
     <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="149"/>
-      <c r="B95" s="149"/>
-      <c r="C95" s="149"/>
-      <c r="D95" s="149"/>
+      <c r="A95" s="163"/>
+      <c r="B95" s="163"/>
+      <c r="C95" s="163"/>
+      <c r="D95" s="163"/>
     </row>
     <row r="96" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="149"/>
-      <c r="B96" s="149"/>
-      <c r="C96" s="149"/>
-      <c r="D96" s="149"/>
+      <c r="A96" s="163"/>
+      <c r="B96" s="163"/>
+      <c r="C96" s="163"/>
+      <c r="D96" s="163"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
@@ -2735,14 +2735,14 @@
       <c r="C106" s="40"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="148" t="s">
+      <c r="A108" s="162" t="s">
         <v>78</v>
       </c>
-      <c r="B108" s="148"/>
+      <c r="B108" s="162"/>
     </row>
     <row r="109" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="148"/>
-      <c r="B109" s="148"/>
+      <c r="A109" s="162"/>
+      <c r="B109" s="162"/>
     </row>
     <row r="110" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="105"/>
@@ -2781,47 +2781,47 @@
       <c r="L117" s="8"/>
     </row>
     <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="147"/>
-      <c r="B118" s="147"/>
-      <c r="C118" s="147"/>
-      <c r="D118" s="147"/>
+      <c r="A118" s="161"/>
+      <c r="B118" s="161"/>
+      <c r="C118" s="161"/>
+      <c r="D118" s="161"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="147"/>
-      <c r="B119" s="147"/>
-      <c r="C119" s="147"/>
-      <c r="D119" s="147"/>
+      <c r="A119" s="161"/>
+      <c r="B119" s="161"/>
+      <c r="C119" s="161"/>
+      <c r="D119" s="161"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="147"/>
-      <c r="B120" s="147"/>
-      <c r="C120" s="147"/>
-      <c r="D120" s="147"/>
+      <c r="A120" s="161"/>
+      <c r="B120" s="161"/>
+      <c r="C120" s="161"/>
+      <c r="D120" s="161"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="147"/>
-      <c r="B121" s="147"/>
-      <c r="C121" s="147"/>
-      <c r="D121" s="147"/>
+      <c r="A121" s="161"/>
+      <c r="B121" s="161"/>
+      <c r="C121" s="161"/>
+      <c r="D121" s="161"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A118:D121"/>
+    <mergeCell ref="A108:B109"/>
+    <mergeCell ref="A94:D96"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="F27:G28"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A118:D121"/>
-    <mergeCell ref="A108:B109"/>
-    <mergeCell ref="A94:D96"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2857,18 +2857,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="170" t="s">
+      <c r="B1" s="164" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2877,39 +2877,39 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="164"/>
+      <c r="J2" s="164"/>
+      <c r="K2" s="164"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="130">
-        <v>8500000</v>
+        <v>9000000</v>
       </c>
       <c r="P2" s="47"/>
       <c r="Q2" s="14"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="171"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="171"/>
-      <c r="K3" s="171"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2919,10 +2919,10 @@
       <c r="P3" s="52"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="164" t="s">
+      <c r="A4" s="178" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="166" t="s">
+      <c r="B4" s="180" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="168" t="s">
@@ -2946,49 +2946,49 @@
       <c r="I4" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="177" t="s">
+      <c r="J4" s="173" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="175" t="s">
+      <c r="K4" s="170" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="175" t="s">
+      <c r="L4" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="175" t="s">
+      <c r="M4" s="170" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="180" t="s">
+      <c r="N4" s="176" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="172" t="s">
+      <c r="P4" s="166" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="40"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="165"/>
-      <c r="B5" s="167"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="169"/>
-      <c r="H5" s="169"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="179"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="181"/>
+      <c r="A5" s="179"/>
+      <c r="B5" s="181"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="174"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="175"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="177"/>
       <c r="O5" s="53" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/11</v>
       </c>
-      <c r="P5" s="173"/>
+      <c r="P5" s="167"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3028,18 +3028,18 @@
       </c>
       <c r="M6" s="67">
         <f>O$2*F6%</f>
-        <v>388450.00000000006</v>
+        <v>411300.00000000006</v>
       </c>
       <c r="N6" s="68">
         <v>0</v>
       </c>
       <c r="O6" s="69">
         <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>398539.01</v>
+        <v>421389.01</v>
       </c>
       <c r="P6" s="70">
         <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
-        <v>410495.01</v>
+        <v>434031.01</v>
       </c>
       <c r="Q6" s="40">
         <v>0.01</v>
@@ -3083,18 +3083,18 @@
       </c>
       <c r="M7" s="67">
         <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
-        <v>260949.99999999997</v>
+        <v>276300</v>
       </c>
       <c r="N7" s="68">
         <v>0</v>
       </c>
       <c r="O7" s="69">
         <f t="shared" si="0"/>
-        <v>494015.02</v>
+        <v>509365.02</v>
       </c>
       <c r="P7" s="70">
         <f t="shared" si="1"/>
-        <v>508835.02</v>
+        <v>524646.02</v>
       </c>
       <c r="Q7" s="40">
         <f>Q6+0.01</f>
@@ -3142,18 +3142,18 @@
       </c>
       <c r="M8" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N8" s="68">
         <v>0</v>
       </c>
       <c r="O8" s="69">
         <f t="shared" si="0"/>
-        <v>2316386.0299999998</v>
+        <v>2339136.0299999998</v>
       </c>
       <c r="P8" s="70">
         <f t="shared" si="1"/>
-        <v>2385878.0299999998</v>
+        <v>2409310.0299999998</v>
       </c>
       <c r="Q8" s="40">
         <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
@@ -3198,18 +3198,18 @@
       </c>
       <c r="M9" s="67">
         <f t="shared" si="5"/>
-        <v>259250</v>
+        <v>274500</v>
       </c>
       <c r="N9" s="68">
         <v>0</v>
       </c>
       <c r="O9" s="69">
         <f t="shared" si="0"/>
-        <v>230729.04</v>
+        <v>245979.04</v>
       </c>
       <c r="P9" s="70">
         <f t="shared" si="1"/>
-        <v>237651.04</v>
+        <v>253358.04</v>
       </c>
       <c r="Q9" s="40">
         <f t="shared" si="6"/>
@@ -3259,18 +3259,18 @@
       </c>
       <c r="M10" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N10" s="68">
         <v>0</v>
       </c>
       <c r="O10" s="69">
         <f t="shared" si="0"/>
-        <v>386598.05</v>
+        <v>409348.05</v>
       </c>
       <c r="P10" s="70">
         <f t="shared" si="1"/>
-        <v>398196.05</v>
+        <v>421628.05</v>
       </c>
       <c r="Q10" s="40">
         <f t="shared" si="6"/>
@@ -3316,18 +3316,18 @@
       </c>
       <c r="M11" s="67">
         <f t="shared" si="5"/>
-        <v>259250</v>
+        <v>274500</v>
       </c>
       <c r="N11" s="68">
         <v>0</v>
       </c>
       <c r="O11" s="69">
         <f t="shared" si="0"/>
-        <v>252845.06</v>
+        <v>268095.06</v>
       </c>
       <c r="P11" s="70">
         <f t="shared" si="1"/>
-        <v>260430.06</v>
+        <v>276138.06</v>
       </c>
       <c r="Q11" s="40">
         <f t="shared" si="6"/>
@@ -3372,18 +3372,18 @@
       </c>
       <c r="M12" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N12" s="68">
         <v>0</v>
       </c>
       <c r="O12" s="69">
         <f t="shared" si="0"/>
-        <v>385250.07</v>
+        <v>408000.07</v>
       </c>
       <c r="P12" s="70">
         <f t="shared" si="1"/>
-        <v>396808.07</v>
+        <v>420240.07</v>
       </c>
       <c r="Q12" s="40">
         <f t="shared" si="6"/>
@@ -3430,18 +3430,18 @@
       </c>
       <c r="M13" s="67">
         <f t="shared" si="5"/>
-        <v>259250</v>
+        <v>274500</v>
       </c>
       <c r="N13" s="68">
         <v>0</v>
       </c>
       <c r="O13" s="69">
         <f t="shared" si="0"/>
-        <v>253445.08</v>
+        <v>268695.08</v>
       </c>
       <c r="P13" s="70">
         <f t="shared" si="1"/>
-        <v>261048.08</v>
+        <v>276756.08</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" si="6"/>
@@ -3487,18 +3487,18 @@
       </c>
       <c r="M14" s="67">
         <f t="shared" si="5"/>
-        <v>387599.99999999994</v>
+        <v>410399.99999999994</v>
       </c>
       <c r="N14" s="68">
         <v>0</v>
       </c>
       <c r="O14" s="69">
         <f t="shared" si="0"/>
-        <v>386800.09</v>
+        <v>409600.09</v>
       </c>
       <c r="P14" s="70">
         <f t="shared" si="1"/>
-        <v>398404.09</v>
+        <v>421888.09</v>
       </c>
       <c r="Q14" s="40">
         <f t="shared" si="6"/>
@@ -3546,18 +3546,18 @@
       </c>
       <c r="M15" s="67">
         <f t="shared" si="5"/>
-        <v>259250</v>
+        <v>274500</v>
       </c>
       <c r="N15" s="68">
         <v>0</v>
       </c>
       <c r="O15" s="69">
         <f t="shared" si="0"/>
-        <v>490680.1</v>
+        <v>505930.1</v>
       </c>
       <c r="P15" s="70">
         <f t="shared" si="1"/>
-        <v>505400.1</v>
+        <v>521108.1</v>
       </c>
       <c r="Q15" s="40">
         <f t="shared" si="6"/>
@@ -3606,18 +3606,18 @@
       </c>
       <c r="M16" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N16" s="68">
         <v>0</v>
       </c>
       <c r="O16" s="69">
         <f t="shared" si="0"/>
-        <v>386750.11</v>
+        <v>409500.11</v>
       </c>
       <c r="P16" s="70">
         <f t="shared" si="1"/>
-        <v>398353.11</v>
+        <v>421785.11</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" si="6"/>
@@ -3663,18 +3663,18 @@
       </c>
       <c r="M17" s="67">
         <f t="shared" si="5"/>
-        <v>259250</v>
+        <v>274500</v>
       </c>
       <c r="N17" s="68">
         <v>0</v>
       </c>
       <c r="O17" s="69">
         <f t="shared" si="0"/>
-        <v>259250.12</v>
+        <v>274500.12</v>
       </c>
       <c r="P17" s="70">
         <f t="shared" si="1"/>
-        <v>267028.12</v>
+        <v>282735.12</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="6"/>
@@ -3719,18 +3719,18 @@
       </c>
       <c r="M18" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N18" s="68">
         <v>0</v>
       </c>
       <c r="O18" s="69">
         <f t="shared" si="0"/>
-        <v>377482.13</v>
+        <v>400232.13</v>
       </c>
       <c r="P18" s="70">
         <f t="shared" si="1"/>
-        <v>388806.13</v>
+        <v>412239.13</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="6"/>
@@ -3775,18 +3775,18 @@
       </c>
       <c r="M19" s="67">
         <f t="shared" si="5"/>
-        <v>270300</v>
+        <v>286200</v>
       </c>
       <c r="N19" s="68">
         <v>0</v>
       </c>
       <c r="O19" s="69">
         <f t="shared" si="0"/>
-        <v>263622.14</v>
+        <v>279522.14</v>
       </c>
       <c r="P19" s="70">
         <f t="shared" si="1"/>
-        <v>271531.14</v>
+        <v>287908.14</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="6"/>
@@ -3832,18 +3832,18 @@
       </c>
       <c r="M20" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N20" s="68">
         <v>0</v>
       </c>
       <c r="O20" s="69">
         <f t="shared" si="0"/>
-        <v>386750.15</v>
+        <v>409500.15</v>
       </c>
       <c r="P20" s="70">
         <f t="shared" si="1"/>
-        <v>398353.15</v>
+        <v>421785.15</v>
       </c>
       <c r="Q20" s="40">
         <f t="shared" si="6"/>
@@ -3888,18 +3888,18 @@
       </c>
       <c r="M21" s="67">
         <f t="shared" si="5"/>
-        <v>269450</v>
+        <v>285300</v>
       </c>
       <c r="N21" s="68">
         <v>0</v>
       </c>
       <c r="O21" s="69">
         <f t="shared" si="0"/>
-        <v>262350.15999999997</v>
+        <v>278200.15999999997</v>
       </c>
       <c r="P21" s="70">
         <f t="shared" si="1"/>
-        <v>270221.15999999997</v>
+        <v>286546.15999999997</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" si="6"/>
@@ -3949,18 +3949,18 @@
       </c>
       <c r="M22" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N22" s="68">
         <v>0</v>
       </c>
       <c r="O22" s="69">
         <f t="shared" si="0"/>
-        <v>386750.17</v>
+        <v>409500.17</v>
       </c>
       <c r="P22" s="70">
         <f t="shared" si="1"/>
-        <v>398353.17</v>
+        <v>421785.17</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="6"/>
@@ -4006,18 +4006,18 @@
       </c>
       <c r="M23" s="67">
         <f t="shared" si="5"/>
-        <v>269450</v>
+        <v>285300</v>
       </c>
       <c r="N23" s="68">
         <v>0</v>
       </c>
       <c r="O23" s="69">
         <f t="shared" si="0"/>
-        <v>269450.18</v>
+        <v>285300.18</v>
       </c>
       <c r="P23" s="70">
         <f t="shared" si="1"/>
-        <v>277534.18</v>
+        <v>293859.18</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="6"/>
@@ -4063,18 +4063,18 @@
       </c>
       <c r="M24" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N24" s="68">
         <v>0</v>
       </c>
       <c r="O24" s="69">
         <f t="shared" si="0"/>
-        <v>386750.19</v>
+        <v>409500.19</v>
       </c>
       <c r="P24" s="70">
         <f t="shared" si="1"/>
-        <v>398353.19</v>
+        <v>421785.19</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" si="6"/>
@@ -4120,18 +4120,18 @@
       </c>
       <c r="M25" s="67">
         <f t="shared" si="5"/>
-        <v>269450</v>
+        <v>285300</v>
       </c>
       <c r="N25" s="68">
         <v>0</v>
       </c>
       <c r="O25" s="69">
         <f t="shared" si="0"/>
-        <v>269450.2</v>
+        <v>285300.2</v>
       </c>
       <c r="P25" s="70">
         <f t="shared" si="1"/>
-        <v>277534.2</v>
+        <v>293859.20000000001</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="6"/>
@@ -4180,18 +4180,18 @@
       </c>
       <c r="M26" s="67">
         <f t="shared" si="5"/>
-        <v>386750</v>
+        <v>409500</v>
       </c>
       <c r="N26" s="68">
         <v>0</v>
       </c>
       <c r="O26" s="69">
         <f t="shared" si="0"/>
-        <v>386750.21</v>
+        <v>409500.21</v>
       </c>
       <c r="P26" s="70">
         <f t="shared" si="1"/>
-        <v>398353.21</v>
+        <v>421785.21</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="6"/>
@@ -4237,18 +4237,18 @@
       </c>
       <c r="M27" s="67">
         <f t="shared" si="5"/>
-        <v>269450</v>
+        <v>285300</v>
       </c>
       <c r="N27" s="68">
         <v>0</v>
       </c>
       <c r="O27" s="69">
         <f t="shared" si="0"/>
-        <v>-53429.78</v>
+        <v>-37579.78</v>
       </c>
       <c r="P27" s="70">
         <f t="shared" si="1"/>
-        <v>-55032.78</v>
+        <v>-38706.78</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="6"/>
@@ -4294,18 +4294,18 @@
       </c>
       <c r="M28" s="67">
         <f t="shared" si="5"/>
-        <v>396100</v>
+        <v>419400</v>
       </c>
       <c r="N28" s="68">
         <v>0</v>
       </c>
       <c r="O28" s="69">
         <f t="shared" si="0"/>
-        <v>396100.23</v>
+        <v>419400.23</v>
       </c>
       <c r="P28" s="70">
         <f t="shared" si="1"/>
-        <v>407983.23</v>
+        <v>431982.23</v>
       </c>
       <c r="Q28" s="40">
         <f t="shared" si="6"/>
@@ -4351,18 +4351,18 @@
       </c>
       <c r="M29" s="67">
         <f t="shared" si="5"/>
-        <v>272850</v>
+        <v>288899.99999999994</v>
       </c>
       <c r="N29" s="68">
         <v>0</v>
       </c>
       <c r="O29" s="69">
         <f t="shared" si="0"/>
-        <v>272850.24</v>
+        <v>288900.24</v>
       </c>
       <c r="P29" s="70">
         <f t="shared" si="1"/>
-        <v>281036.24</v>
+        <v>297567.24</v>
       </c>
       <c r="Q29" s="40">
         <f t="shared" si="6"/>
@@ -4407,18 +4407,18 @@
       </c>
       <c r="M30" s="67">
         <f t="shared" si="5"/>
-        <v>398650.00000000006</v>
+        <v>422100.00000000006</v>
       </c>
       <c r="N30" s="68">
         <v>0</v>
       </c>
       <c r="O30" s="69">
         <f t="shared" si="0"/>
-        <v>388801.25</v>
+        <v>412251.25</v>
       </c>
       <c r="P30" s="70">
         <f t="shared" si="1"/>
-        <v>400465.25</v>
+        <v>424619.25</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="6"/>
@@ -4467,18 +4467,18 @@
       </c>
       <c r="M31" s="67">
         <f t="shared" si="5"/>
-        <v>256700</v>
+        <v>271800</v>
       </c>
       <c r="N31" s="68">
         <v>0</v>
       </c>
       <c r="O31" s="69">
         <f t="shared" si="0"/>
-        <v>256700.26</v>
+        <v>271800.26</v>
       </c>
       <c r="P31" s="70">
         <f t="shared" si="1"/>
-        <v>264401.26</v>
+        <v>279954.26</v>
       </c>
       <c r="Q31" s="121">
         <f t="shared" si="6"/>
@@ -4528,18 +4528,18 @@
       </c>
       <c r="M32" s="67">
         <f>O$2*F32%</f>
-        <v>13600</v>
+        <v>14400</v>
       </c>
       <c r="N32" s="68">
         <v>0</v>
       </c>
       <c r="O32" s="69">
         <f t="shared" si="0"/>
-        <v>13600.27</v>
+        <v>14400.27</v>
       </c>
       <c r="P32" s="70">
         <f t="shared" si="1"/>
-        <v>14008.27</v>
+        <v>14832.27</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="6"/>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="M34" s="54">
         <f>SUM(M6:M33)</f>
-        <v>8500000</v>
+        <v>9000000</v>
       </c>
       <c r="N34" s="54">
         <f>SUM(N6:N33)</f>
@@ -4629,11 +4629,11 @@
       </c>
       <c r="O34" s="80">
         <f>SUM(O6:O32)</f>
-        <v>10505265.779999999</v>
+        <v>11005265.779999999</v>
       </c>
       <c r="P34" s="80">
         <f>SUM(P6:P32)</f>
-        <v>10820427.779999999</v>
+        <v>11335424.779999999</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4642,93 +4642,98 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="147" t="s">
+      <c r="D37" s="161" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="147"/>
-      <c r="F37" s="147"/>
-      <c r="G37" s="147"/>
-      <c r="H37" s="147"/>
-      <c r="I37" s="147"/>
-      <c r="J37" s="147"/>
-      <c r="K37" s="147"/>
-      <c r="L37" s="147"/>
-      <c r="M37" s="147"/>
-      <c r="N37" s="147"/>
-      <c r="O37" s="147"/>
+      <c r="E37" s="161"/>
+      <c r="F37" s="161"/>
+      <c r="G37" s="161"/>
+      <c r="H37" s="161"/>
+      <c r="I37" s="161"/>
+      <c r="J37" s="161"/>
+      <c r="K37" s="161"/>
+      <c r="L37" s="161"/>
+      <c r="M37" s="161"/>
+      <c r="N37" s="161"/>
+      <c r="O37" s="161"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="147"/>
-      <c r="E38" s="147"/>
-      <c r="F38" s="147"/>
-      <c r="G38" s="147"/>
-      <c r="H38" s="147"/>
-      <c r="I38" s="147"/>
-      <c r="J38" s="147"/>
-      <c r="K38" s="147"/>
-      <c r="L38" s="147"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="147"/>
-      <c r="O38" s="147"/>
+      <c r="D38" s="161"/>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="161"/>
+      <c r="L38" s="161"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="161"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="147"/>
-      <c r="E39" s="147"/>
-      <c r="F39" s="147"/>
-      <c r="G39" s="147"/>
-      <c r="H39" s="147"/>
-      <c r="I39" s="147"/>
-      <c r="J39" s="147"/>
-      <c r="K39" s="147"/>
-      <c r="L39" s="147"/>
-      <c r="M39" s="147"/>
-      <c r="N39" s="147"/>
-      <c r="O39" s="147"/>
+      <c r="D39" s="161"/>
+      <c r="E39" s="161"/>
+      <c r="F39" s="161"/>
+      <c r="G39" s="161"/>
+      <c r="H39" s="161"/>
+      <c r="I39" s="161"/>
+      <c r="J39" s="161"/>
+      <c r="K39" s="161"/>
+      <c r="L39" s="161"/>
+      <c r="M39" s="161"/>
+      <c r="N39" s="161"/>
+      <c r="O39" s="161"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="147"/>
-      <c r="E40" s="147"/>
-      <c r="F40" s="147"/>
-      <c r="G40" s="147"/>
-      <c r="H40" s="147"/>
-      <c r="I40" s="147"/>
-      <c r="J40" s="147"/>
-      <c r="K40" s="147"/>
-      <c r="L40" s="147"/>
-      <c r="M40" s="147"/>
-      <c r="N40" s="147"/>
-      <c r="O40" s="147"/>
+      <c r="D40" s="161"/>
+      <c r="E40" s="161"/>
+      <c r="F40" s="161"/>
+      <c r="G40" s="161"/>
+      <c r="H40" s="161"/>
+      <c r="I40" s="161"/>
+      <c r="J40" s="161"/>
+      <c r="K40" s="161"/>
+      <c r="L40" s="161"/>
+      <c r="M40" s="161"/>
+      <c r="N40" s="161"/>
+      <c r="O40" s="161"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="147"/>
-      <c r="E41" s="147"/>
-      <c r="F41" s="147"/>
-      <c r="G41" s="147"/>
-      <c r="H41" s="147"/>
-      <c r="I41" s="147"/>
-      <c r="J41" s="147"/>
-      <c r="K41" s="147"/>
-      <c r="L41" s="147"/>
-      <c r="M41" s="147"/>
-      <c r="N41" s="147"/>
-      <c r="O41" s="147"/>
+      <c r="D41" s="161"/>
+      <c r="E41" s="161"/>
+      <c r="F41" s="161"/>
+      <c r="G41" s="161"/>
+      <c r="H41" s="161"/>
+      <c r="I41" s="161"/>
+      <c r="J41" s="161"/>
+      <c r="K41" s="161"/>
+      <c r="L41" s="161"/>
+      <c r="M41" s="161"/>
+      <c r="N41" s="161"/>
+      <c r="O41" s="161"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
-      <c r="G42" s="147"/>
-      <c r="H42" s="147"/>
-      <c r="I42" s="147"/>
-      <c r="J42" s="147"/>
-      <c r="K42" s="147"/>
-      <c r="L42" s="147"/>
-      <c r="M42" s="147"/>
-      <c r="N42" s="147"/>
-      <c r="O42" s="147"/>
+      <c r="D42" s="161"/>
+      <c r="E42" s="161"/>
+      <c r="F42" s="161"/>
+      <c r="G42" s="161"/>
+      <c r="H42" s="161"/>
+      <c r="I42" s="161"/>
+      <c r="J42" s="161"/>
+      <c r="K42" s="161"/>
+      <c r="L42" s="161"/>
+      <c r="M42" s="161"/>
+      <c r="N42" s="161"/>
+      <c r="O42" s="161"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4741,11 +4746,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
